--- a/Excel/Excercises/Logical.xlsx
+++ b/Excel/Excercises/Logical.xlsx
@@ -1,19 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F687E566-0AB3-468C-ACE3-727FC0449F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exercise" sheetId="2" r:id="rId1"/>
     <sheet name="Practice" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -130,7 +142,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -378,7 +390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -392,16 +404,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -409,7 +420,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{7007B6CF-4EFB-45BC-80D1-33605F9C1B60}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -683,19 +696,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:L10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="21" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:12" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" ht="18" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
@@ -710,7 +723,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -723,7 +736,7 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4">
         <v>1</v>
       </c>
@@ -740,7 +753,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="4">
         <v>2</v>
       </c>
@@ -757,7 +770,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="4">
         <v>3</v>
       </c>
@@ -774,7 +787,7 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4">
         <v>4</v>
       </c>
@@ -791,7 +804,7 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="4"/>
       <c r="C10" s="2"/>
       <c r="D10" s="3"/>
@@ -810,27 +823,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:P1003"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.42578125" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.28515625" customWidth="1"/>
+    <col min="14" max="14" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="10" t="s">
         <v>25</v>
       </c>
@@ -864,12 +877,8 @@
       <c r="L3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>5</v>
       </c>
@@ -894,12 +903,12 @@
       <c r="I4" s="5">
         <v>74</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="O4" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P4" s="18"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P4" s="17"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
         <v>5</v>
       </c>
@@ -924,13 +933,13 @@
       <c r="I5" s="5">
         <v>88</v>
       </c>
-      <c r="O5" s="15" t="str">
+      <c r="O5" s="14" t="str">
         <f>"A"</f>
         <v>A</v>
       </c>
-      <c r="P5" s="13"/>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P5" s="12"/>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
@@ -955,13 +964,13 @@
       <c r="I6" s="5">
         <v>93</v>
       </c>
-      <c r="O6" s="15" t="str">
+      <c r="O6" s="14" t="str">
         <f>"B"</f>
         <v>B</v>
       </c>
-      <c r="P6" s="13"/>
-    </row>
-    <row r="7" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P6" s="12"/>
+    </row>
+    <row r="7" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="8" t="s">
         <v>10</v>
       </c>
@@ -986,13 +995,13 @@
       <c r="I7" s="5">
         <v>44</v>
       </c>
-      <c r="O7" s="16" t="str">
+      <c r="O7" s="15" t="str">
         <f>"C"</f>
         <v>C</v>
       </c>
-      <c r="P7" s="14"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P7" s="13"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
@@ -1018,7 +1027,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="8" t="s">
         <v>5</v>
       </c>
@@ -1044,7 +1053,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>5</v>
       </c>
@@ -1070,7 +1079,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -1096,7 +1105,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>10</v>
       </c>
@@ -1122,7 +1131,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>5</v>
       </c>
@@ -1148,7 +1157,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>10</v>
       </c>
@@ -1174,7 +1183,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="8" t="s">
         <v>10</v>
       </c>
@@ -1200,7 +1209,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="s">
         <v>5</v>
       </c>
@@ -1226,7 +1235,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="8" t="s">
         <v>10</v>
       </c>
@@ -1252,7 +1261,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
@@ -1278,7 +1287,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="s">
         <v>5</v>
       </c>
@@ -1304,7 +1313,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>10</v>
       </c>
@@ -1330,7 +1339,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>5</v>
       </c>
@@ -1356,7 +1365,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>10</v>
       </c>
@@ -1382,7 +1391,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>5</v>
       </c>
@@ -1408,7 +1417,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="8" t="s">
         <v>10</v>
       </c>
@@ -1434,7 +1443,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
         <v>5</v>
       </c>
@@ -1460,7 +1469,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="8" t="s">
         <v>10</v>
       </c>
@@ -1486,7 +1495,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
         <v>5</v>
       </c>
@@ -1512,7 +1521,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>10</v>
       </c>
@@ -1538,7 +1547,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
         <v>10</v>
       </c>
@@ -1564,7 +1573,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="8" t="s">
         <v>10</v>
       </c>
@@ -1590,7 +1599,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>5</v>
       </c>
@@ -1616,7 +1625,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>10</v>
       </c>
@@ -1642,7 +1651,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
         <v>5</v>
       </c>
@@ -1668,7 +1677,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
         <v>5</v>
       </c>
@@ -1694,7 +1703,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="8" t="s">
         <v>5</v>
       </c>
@@ -1720,7 +1729,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36" s="8" t="s">
         <v>5</v>
       </c>
@@ -1746,7 +1755,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37" s="8" t="s">
         <v>10</v>
       </c>
@@ -1772,7 +1781,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="8" t="s">
         <v>10</v>
       </c>
@@ -1798,7 +1807,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="8" t="s">
         <v>10</v>
       </c>
@@ -1824,7 +1833,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40" s="8" t="s">
         <v>5</v>
       </c>
@@ -1850,7 +1859,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41" s="8" t="s">
         <v>5</v>
       </c>
@@ -1876,7 +1885,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42" s="8" t="s">
         <v>5</v>
       </c>
@@ -1902,7 +1911,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43" s="8" t="s">
         <v>10</v>
       </c>
@@ -1928,7 +1937,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44" s="8" t="s">
         <v>10</v>
       </c>
@@ -1954,7 +1963,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45" s="8" t="s">
         <v>5</v>
       </c>
@@ -1980,7 +1989,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46" s="8" t="s">
         <v>5</v>
       </c>
@@ -2006,7 +2015,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47" s="8" t="s">
         <v>10</v>
       </c>
@@ -2032,7 +2041,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48" s="8" t="s">
         <v>5</v>
       </c>
@@ -2058,7 +2067,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49" s="8" t="s">
         <v>10</v>
       </c>
@@ -2084,7 +2093,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50" s="8" t="s">
         <v>5</v>
       </c>
@@ -2110,7 +2119,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51" s="8" t="s">
         <v>5</v>
       </c>
@@ -2136,7 +2145,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52" s="8" t="s">
         <v>5</v>
       </c>
@@ -2162,7 +2171,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53" s="8" t="s">
         <v>10</v>
       </c>
@@ -2188,7 +2197,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54" s="8" t="s">
         <v>10</v>
       </c>
@@ -2214,7 +2223,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="s">
         <v>10</v>
       </c>
@@ -2240,7 +2249,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="8" t="s">
         <v>10</v>
       </c>
@@ -2266,7 +2275,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57" s="8" t="s">
         <v>10</v>
       </c>
@@ -2292,7 +2301,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
         <v>5</v>
       </c>
@@ -2318,7 +2327,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59" s="8" t="s">
         <v>5</v>
       </c>
@@ -2344,7 +2353,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60" s="8" t="s">
         <v>5</v>
       </c>
@@ -2370,7 +2379,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="8" t="s">
         <v>10</v>
       </c>
@@ -2396,7 +2405,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="8" t="s">
         <v>10</v>
       </c>
@@ -2422,7 +2431,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="8" t="s">
         <v>5</v>
       </c>
@@ -2448,7 +2457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64" s="8" t="s">
         <v>10</v>
       </c>
@@ -2474,7 +2483,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65" s="8" t="s">
         <v>10</v>
       </c>
@@ -2500,7 +2509,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66" s="8" t="s">
         <v>10</v>
       </c>
@@ -2526,7 +2535,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67" s="8" t="s">
         <v>5</v>
       </c>
@@ -2552,7 +2561,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="8" t="s">
         <v>5</v>
       </c>
@@ -2578,7 +2587,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="8" t="s">
         <v>10</v>
       </c>
@@ -2604,7 +2613,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="8" t="s">
         <v>10</v>
       </c>
@@ -2630,7 +2639,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71" s="8" t="s">
         <v>5</v>
       </c>
@@ -2656,7 +2665,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72" s="8" t="s">
         <v>10</v>
       </c>
@@ -2682,7 +2691,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73" s="8" t="s">
         <v>5</v>
       </c>
@@ -2708,7 +2717,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="8" t="s">
         <v>5</v>
       </c>
@@ -2734,7 +2743,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75" s="8" t="s">
         <v>10</v>
       </c>
@@ -2760,7 +2769,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76" s="8" t="s">
         <v>5</v>
       </c>
@@ -2786,7 +2795,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="8" t="s">
         <v>10</v>
       </c>
@@ -2812,7 +2821,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="8" t="s">
         <v>10</v>
       </c>
@@ -2838,7 +2847,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79" s="8" t="s">
         <v>10</v>
       </c>
@@ -2864,7 +2873,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80" s="8" t="s">
         <v>10</v>
       </c>
@@ -2890,7 +2899,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="8" t="s">
         <v>10</v>
       </c>
@@ -2916,7 +2925,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82" s="8" t="s">
         <v>5</v>
       </c>
@@ -2942,7 +2951,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83" s="8" t="s">
         <v>5</v>
       </c>
@@ -2968,7 +2977,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84" s="8" t="s">
         <v>5</v>
       </c>
@@ -2994,7 +3003,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="8" t="s">
         <v>10</v>
       </c>
@@ -3020,7 +3029,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86" s="8" t="s">
         <v>10</v>
       </c>
@@ -3046,7 +3055,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87" s="8" t="s">
         <v>10</v>
       </c>
@@ -3072,7 +3081,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88" s="8" t="s">
         <v>10</v>
       </c>
@@ -3098,7 +3107,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89" s="8" t="s">
         <v>5</v>
       </c>
@@ -3124,7 +3133,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B90" s="8" t="s">
         <v>5</v>
       </c>
@@ -3150,7 +3159,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91" s="8" t="s">
         <v>5</v>
       </c>
@@ -3176,7 +3185,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92" s="8" t="s">
         <v>5</v>
       </c>
@@ -3202,7 +3211,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93" s="8" t="s">
         <v>5</v>
       </c>
@@ -3228,7 +3237,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94" s="8" t="s">
         <v>5</v>
       </c>
@@ -3254,7 +3263,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95" s="8" t="s">
         <v>10</v>
       </c>
@@ -3280,7 +3289,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B96" s="8" t="s">
         <v>10</v>
       </c>
@@ -3306,7 +3315,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B97" s="8" t="s">
         <v>10</v>
       </c>
@@ -3332,7 +3341,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B98" s="8" t="s">
         <v>5</v>
       </c>
@@ -3358,7 +3367,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99" s="8" t="s">
         <v>10</v>
       </c>
@@ -3384,7 +3393,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100" s="8" t="s">
         <v>10</v>
       </c>
@@ -3410,7 +3419,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
@@ -3436,7 +3445,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B102" s="8" t="s">
         <v>5</v>
       </c>
@@ -3462,7 +3471,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B103" s="8" t="s">
         <v>5</v>
       </c>
@@ -3488,7 +3497,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B104" s="8" t="s">
         <v>10</v>
       </c>
@@ -3514,7 +3523,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B105" s="8" t="s">
         <v>10</v>
       </c>
@@ -3540,7 +3549,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B106" s="8" t="s">
         <v>5</v>
       </c>
@@ -3566,7 +3575,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B107" s="8" t="s">
         <v>10</v>
       </c>
@@ -3592,7 +3601,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B108" s="8" t="s">
         <v>10</v>
       </c>
@@ -3618,7 +3627,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B109" s="8" t="s">
         <v>5</v>
       </c>
@@ -3644,7 +3653,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B110" s="8" t="s">
         <v>5</v>
       </c>
@@ -3670,7 +3679,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B111" s="8" t="s">
         <v>10</v>
       </c>
@@ -3696,7 +3705,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B112" s="8" t="s">
         <v>5</v>
       </c>
@@ -3722,7 +3731,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B113" s="8" t="s">
         <v>5</v>
       </c>
@@ -3748,7 +3757,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
         <v>5</v>
       </c>
@@ -3774,7 +3783,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B115" s="8" t="s">
         <v>10</v>
       </c>
@@ -3800,7 +3809,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B116" s="8" t="s">
         <v>10</v>
       </c>
@@ -3826,7 +3835,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B117" s="8" t="s">
         <v>5</v>
       </c>
@@ -3852,7 +3861,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B118" s="8" t="s">
         <v>5</v>
       </c>
@@ -3878,7 +3887,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B119" s="8" t="s">
         <v>10</v>
       </c>
@@ -3904,7 +3913,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B120" s="8" t="s">
         <v>5</v>
       </c>
@@ -3930,7 +3939,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B121" s="8" t="s">
         <v>5</v>
       </c>
@@ -3956,7 +3965,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B122" s="8" t="s">
         <v>5</v>
       </c>
@@ -3982,7 +3991,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B123" s="8" t="s">
         <v>5</v>
       </c>
@@ -4008,7 +4017,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B124" s="8" t="s">
         <v>5</v>
       </c>
@@ -4034,7 +4043,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B125" s="8" t="s">
         <v>10</v>
       </c>
@@ -4060,7 +4069,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B126" s="8" t="s">
         <v>5</v>
       </c>
@@ -4086,7 +4095,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B127" s="8" t="s">
         <v>10</v>
       </c>
@@ -4112,7 +4121,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B128" s="8" t="s">
         <v>10</v>
       </c>
@@ -4138,7 +4147,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B129" s="8" t="s">
         <v>5</v>
       </c>
@@ -4164,7 +4173,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B130" s="8" t="s">
         <v>10</v>
       </c>
@@ -4190,7 +4199,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B131" s="8" t="s">
         <v>10</v>
       </c>
@@ -4216,7 +4225,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B132" s="8" t="s">
         <v>10</v>
       </c>
@@ -4242,7 +4251,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B133" s="8" t="s">
         <v>5</v>
       </c>
@@ -4268,7 +4277,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B134" s="8" t="s">
         <v>10</v>
       </c>
@@ -4294,7 +4303,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B135" s="8" t="s">
         <v>10</v>
       </c>
@@ -4320,7 +4329,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B136" s="8" t="s">
         <v>10</v>
       </c>
@@ -4346,7 +4355,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B137" s="8" t="s">
         <v>5</v>
       </c>
@@ -4372,7 +4381,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B138" s="8" t="s">
         <v>10</v>
       </c>
@@ -4398,7 +4407,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B139" s="8" t="s">
         <v>10</v>
       </c>
@@ -4424,7 +4433,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B140" s="8" t="s">
         <v>10</v>
       </c>
@@ -4450,7 +4459,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B141" s="8" t="s">
         <v>10</v>
       </c>
@@ -4476,7 +4485,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B142" s="8" t="s">
         <v>5</v>
       </c>
@@ -4502,7 +4511,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B143" s="8" t="s">
         <v>10</v>
       </c>
@@ -4528,7 +4537,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B144" s="8" t="s">
         <v>5</v>
       </c>
@@ -4554,7 +4563,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B145" s="8" t="s">
         <v>5</v>
       </c>
@@ -4580,7 +4589,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B146" s="8" t="s">
         <v>5</v>
       </c>
@@ -4606,7 +4615,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B147" s="8" t="s">
         <v>10</v>
       </c>
@@ -4632,7 +4641,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B148" s="8" t="s">
         <v>10</v>
       </c>
@@ -4658,7 +4667,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B149" s="8" t="s">
         <v>5</v>
       </c>
@@ -4684,7 +4693,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B150" s="8" t="s">
         <v>10</v>
       </c>
@@ -4710,7 +4719,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B151" s="8" t="s">
         <v>10</v>
       </c>
@@ -4736,7 +4745,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B152" s="8" t="s">
         <v>5</v>
       </c>
@@ -4762,7 +4771,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B153" s="8" t="s">
         <v>10</v>
       </c>
@@ -4788,7 +4797,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B154" s="8" t="s">
         <v>10</v>
       </c>
@@ -4814,7 +4823,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B155" s="8" t="s">
         <v>10</v>
       </c>
@@ -4840,7 +4849,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B156" s="8" t="s">
         <v>5</v>
       </c>
@@ -4866,7 +4875,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B157" s="8" t="s">
         <v>10</v>
       </c>
@@ -4892,7 +4901,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B158" s="8" t="s">
         <v>10</v>
       </c>
@@ -4918,7 +4927,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B159" s="8" t="s">
         <v>5</v>
       </c>
@@ -4944,7 +4953,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B160" s="8" t="s">
         <v>5</v>
       </c>
@@ -4970,7 +4979,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B161" s="8" t="s">
         <v>10</v>
       </c>
@@ -4996,7 +5005,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B162" s="8" t="s">
         <v>5</v>
       </c>
@@ -5022,7 +5031,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B163" s="8" t="s">
         <v>10</v>
       </c>
@@ -5048,7 +5057,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B164" s="8" t="s">
         <v>10</v>
       </c>
@@ -5074,7 +5083,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B165" s="8" t="s">
         <v>5</v>
       </c>
@@ -5100,7 +5109,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B166" s="8" t="s">
         <v>10</v>
       </c>
@@ -5126,7 +5135,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B167" s="8" t="s">
         <v>10</v>
       </c>
@@ -5152,7 +5161,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B168" s="8" t="s">
         <v>5</v>
       </c>
@@ -5178,7 +5187,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B169" s="8" t="s">
         <v>5</v>
       </c>
@@ -5204,7 +5213,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B170" s="8" t="s">
         <v>10</v>
       </c>
@@ -5230,7 +5239,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B171" s="8" t="s">
         <v>5</v>
       </c>
@@ -5256,7 +5265,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B172" s="8" t="s">
         <v>5</v>
       </c>
@@ -5282,7 +5291,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B173" s="8" t="s">
         <v>5</v>
       </c>
@@ -5308,7 +5317,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B174" s="8" t="s">
         <v>10</v>
       </c>
@@ -5334,7 +5343,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B175" s="8" t="s">
         <v>10</v>
       </c>
@@ -5360,7 +5369,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B176" s="8" t="s">
         <v>5</v>
       </c>
@@ -5386,7 +5395,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B177" s="8" t="s">
         <v>5</v>
       </c>
@@ -5412,7 +5421,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B178" s="8" t="s">
         <v>5</v>
       </c>
@@ -5438,7 +5447,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B179" s="8" t="s">
         <v>5</v>
       </c>
@@ -5464,7 +5473,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B180" s="8" t="s">
         <v>5</v>
       </c>
@@ -5490,7 +5499,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B181" s="8" t="s">
         <v>5</v>
       </c>
@@ -5516,7 +5525,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B182" s="8" t="s">
         <v>5</v>
       </c>
@@ -5542,7 +5551,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B183" s="8" t="s">
         <v>5</v>
       </c>
@@ -5568,7 +5577,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B184" s="8" t="s">
         <v>10</v>
       </c>
@@ -5594,7 +5603,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B185" s="8" t="s">
         <v>5</v>
       </c>
@@ -5620,7 +5629,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B186" s="8" t="s">
         <v>5</v>
       </c>
@@ -5646,7 +5655,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B187" s="8" t="s">
         <v>5</v>
       </c>
@@ -5672,7 +5681,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B188" s="8" t="s">
         <v>10</v>
       </c>
@@ -5698,7 +5707,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B189" s="8" t="s">
         <v>10</v>
       </c>
@@ -5724,7 +5733,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B190" s="8" t="s">
         <v>10</v>
       </c>
@@ -5750,7 +5759,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B191" s="8" t="s">
         <v>10</v>
       </c>
@@ -5776,7 +5785,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B192" s="8" t="s">
         <v>10</v>
       </c>
@@ -5802,7 +5811,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B193" s="8" t="s">
         <v>5</v>
       </c>
@@ -5828,7 +5837,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B194" s="8" t="s">
         <v>5</v>
       </c>
@@ -5854,7 +5863,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B195" s="8" t="s">
         <v>10</v>
       </c>
@@ -5880,7 +5889,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B196" s="8" t="s">
         <v>5</v>
       </c>
@@ -5906,7 +5915,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B197" s="8" t="s">
         <v>10</v>
       </c>
@@ -5932,7 +5941,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B198" s="8" t="s">
         <v>5</v>
       </c>
@@ -5958,7 +5967,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B199" s="8" t="s">
         <v>10</v>
       </c>
@@ -5984,7 +5993,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B200" s="8" t="s">
         <v>10</v>
       </c>
@@ -6010,7 +6019,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B201" s="8" t="s">
         <v>10</v>
       </c>
@@ -6036,7 +6045,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B202" s="8" t="s">
         <v>5</v>
       </c>
@@ -6062,7 +6071,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="203" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B203" s="8" t="s">
         <v>5</v>
       </c>
@@ -6088,7 +6097,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="204" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B204" s="8" t="s">
         <v>5</v>
       </c>
@@ -6114,7 +6123,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="205" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B205" s="8" t="s">
         <v>5</v>
       </c>
@@ -6140,7 +6149,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="206" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B206" s="8" t="s">
         <v>10</v>
       </c>
@@ -6166,7 +6175,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="207" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B207" s="8" t="s">
         <v>5</v>
       </c>
@@ -6192,7 +6201,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="208" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B208" s="8" t="s">
         <v>10</v>
       </c>
@@ -6218,7 +6227,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="209" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B209" s="8" t="s">
         <v>10</v>
       </c>
@@ -6244,7 +6253,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="210" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B210" s="8" t="s">
         <v>10</v>
       </c>
@@ -6270,7 +6279,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="211" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B211" s="8" t="s">
         <v>10</v>
       </c>
@@ -6296,7 +6305,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="212" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B212" s="8" t="s">
         <v>5</v>
       </c>
@@ -6322,7 +6331,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="213" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B213" s="8" t="s">
         <v>5</v>
       </c>
@@ -6348,7 +6357,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="214" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B214" s="8" t="s">
         <v>10</v>
       </c>
@@ -6374,7 +6383,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="215" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B215" s="8" t="s">
         <v>10</v>
       </c>
@@ -6400,7 +6409,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="216" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B216" s="8" t="s">
         <v>5</v>
       </c>
@@ -6426,7 +6435,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="217" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B217" s="8" t="s">
         <v>10</v>
       </c>
@@ -6452,7 +6461,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="218" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B218" s="8" t="s">
         <v>10</v>
       </c>
@@ -6478,7 +6487,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="219" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B219" s="8" t="s">
         <v>10</v>
       </c>
@@ -6504,7 +6513,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="220" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B220" s="8" t="s">
         <v>5</v>
       </c>
@@ -6530,7 +6539,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="221" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B221" s="8" t="s">
         <v>5</v>
       </c>
@@ -6556,7 +6565,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="222" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B222" s="8" t="s">
         <v>10</v>
       </c>
@@ -6582,7 +6591,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="223" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B223" s="8" t="s">
         <v>10</v>
       </c>
@@ -6608,7 +6617,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="224" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B224" s="8" t="s">
         <v>5</v>
       </c>
@@ -6634,7 +6643,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="225" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B225" s="8" t="s">
         <v>10</v>
       </c>
@@ -6660,7 +6669,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="226" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B226" s="8" t="s">
         <v>5</v>
       </c>
@@ -6686,7 +6695,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="227" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B227" s="8" t="s">
         <v>10</v>
       </c>
@@ -6712,7 +6721,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="228" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B228" s="8" t="s">
         <v>5</v>
       </c>
@@ -6738,7 +6747,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="229" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B229" s="8" t="s">
         <v>5</v>
       </c>
@@ -6764,7 +6773,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="230" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B230" s="8" t="s">
         <v>5</v>
       </c>
@@ -6790,7 +6799,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="231" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B231" s="8" t="s">
         <v>10</v>
       </c>
@@ -6816,7 +6825,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="232" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B232" s="8" t="s">
         <v>10</v>
       </c>
@@ -6842,7 +6851,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="233" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B233" s="8" t="s">
         <v>5</v>
       </c>
@@ -6868,7 +6877,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="234" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B234" s="8" t="s">
         <v>10</v>
       </c>
@@ -6894,7 +6903,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="235" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B235" s="8" t="s">
         <v>10</v>
       </c>
@@ -6920,7 +6929,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="236" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B236" s="8" t="s">
         <v>5</v>
       </c>
@@ -6946,7 +6955,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="237" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B237" s="8" t="s">
         <v>10</v>
       </c>
@@ -6972,7 +6981,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="238" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B238" s="8" t="s">
         <v>10</v>
       </c>
@@ -6998,7 +7007,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="239" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B239" s="8" t="s">
         <v>10</v>
       </c>
@@ -7024,7 +7033,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="240" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B240" s="8" t="s">
         <v>10</v>
       </c>
@@ -7050,7 +7059,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="241" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B241" s="8" t="s">
         <v>5</v>
       </c>
@@ -7076,7 +7085,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="242" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B242" s="8" t="s">
         <v>10</v>
       </c>
@@ -7102,7 +7111,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="243" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B243" s="8" t="s">
         <v>10</v>
       </c>
@@ -7128,7 +7137,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="244" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B244" s="8" t="s">
         <v>10</v>
       </c>
@@ -7154,7 +7163,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="245" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B245" s="8" t="s">
         <v>5</v>
       </c>
@@ -7180,7 +7189,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="246" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B246" s="8" t="s">
         <v>5</v>
       </c>
@@ -7206,7 +7215,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="247" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B247" s="8" t="s">
         <v>10</v>
       </c>
@@ -7232,7 +7241,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="248" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B248" s="8" t="s">
         <v>10</v>
       </c>
@@ -7258,7 +7267,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="249" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B249" s="8" t="s">
         <v>10</v>
       </c>
@@ -7284,7 +7293,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="250" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B250" s="8" t="s">
         <v>10</v>
       </c>
@@ -7310,7 +7319,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="251" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B251" s="8" t="s">
         <v>5</v>
       </c>
@@ -7336,7 +7345,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="252" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B252" s="8" t="s">
         <v>5</v>
       </c>
@@ -7362,7 +7371,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="253" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B253" s="8" t="s">
         <v>10</v>
       </c>
@@ -7388,7 +7397,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="254" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B254" s="8" t="s">
         <v>10</v>
       </c>
@@ -7414,7 +7423,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="255" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B255" s="8" t="s">
         <v>5</v>
       </c>
@@ -7440,7 +7449,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="256" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B256" s="8" t="s">
         <v>5</v>
       </c>
@@ -7466,7 +7475,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="257" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B257" s="8" t="s">
         <v>10</v>
       </c>
@@ -7492,7 +7501,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="258" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B258" s="8" t="s">
         <v>10</v>
       </c>
@@ -7518,7 +7527,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="259" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B259" s="8" t="s">
         <v>5</v>
       </c>
@@ -7544,7 +7553,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="260" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B260" s="8" t="s">
         <v>5</v>
       </c>
@@ -7570,7 +7579,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="261" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B261" s="8" t="s">
         <v>10</v>
       </c>
@@ -7596,7 +7605,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="262" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B262" s="8" t="s">
         <v>5</v>
       </c>
@@ -7622,7 +7631,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="263" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B263" s="8" t="s">
         <v>5</v>
       </c>
@@ -7648,7 +7657,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="264" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B264" s="8" t="s">
         <v>5</v>
       </c>
@@ -7674,7 +7683,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="265" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B265" s="8" t="s">
         <v>10</v>
       </c>
@@ -7700,7 +7709,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="266" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B266" s="8" t="s">
         <v>5</v>
       </c>
@@ -7726,7 +7735,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="267" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B267" s="8" t="s">
         <v>5</v>
       </c>
@@ -7752,7 +7761,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="268" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B268" s="8" t="s">
         <v>10</v>
       </c>
@@ -7778,7 +7787,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="269" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B269" s="8" t="s">
         <v>10</v>
       </c>
@@ -7804,7 +7813,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="270" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B270" s="8" t="s">
         <v>5</v>
       </c>
@@ -7830,7 +7839,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="271" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B271" s="8" t="s">
         <v>5</v>
       </c>
@@ -7856,7 +7865,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="272" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B272" s="8" t="s">
         <v>5</v>
       </c>
@@ -7882,7 +7891,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="273" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B273" s="8" t="s">
         <v>5</v>
       </c>
@@ -7908,7 +7917,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="274" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B274" s="8" t="s">
         <v>10</v>
       </c>
@@ -7934,7 +7943,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="275" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B275" s="8" t="s">
         <v>10</v>
       </c>
@@ -7960,7 +7969,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="276" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B276" s="8" t="s">
         <v>5</v>
       </c>
@@ -7986,7 +7995,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="277" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B277" s="8" t="s">
         <v>5</v>
       </c>
@@ -8012,7 +8021,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="278" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B278" s="8" t="s">
         <v>10</v>
       </c>
@@ -8038,7 +8047,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="279" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B279" s="8" t="s">
         <v>10</v>
       </c>
@@ -8064,7 +8073,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="280" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B280" s="8" t="s">
         <v>5</v>
       </c>
@@ -8090,7 +8099,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="281" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B281" s="8" t="s">
         <v>5</v>
       </c>
@@ -8116,7 +8125,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="282" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B282" s="8" t="s">
         <v>5</v>
       </c>
@@ -8142,7 +8151,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="283" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B283" s="8" t="s">
         <v>10</v>
       </c>
@@ -8168,7 +8177,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="284" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B284" s="8" t="s">
         <v>10</v>
       </c>
@@ -8194,7 +8203,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="285" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B285" s="8" t="s">
         <v>10</v>
       </c>
@@ -8220,7 +8229,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="286" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B286" s="8" t="s">
         <v>5</v>
       </c>
@@ -8246,7 +8255,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="287" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B287" s="8" t="s">
         <v>5</v>
       </c>
@@ -8272,7 +8281,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="288" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B288" s="8" t="s">
         <v>5</v>
       </c>
@@ -8298,7 +8307,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="289" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B289" s="8" t="s">
         <v>10</v>
       </c>
@@ -8324,7 +8333,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="290" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B290" s="8" t="s">
         <v>10</v>
       </c>
@@ -8350,7 +8359,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="291" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B291" s="8" t="s">
         <v>5</v>
       </c>
@@ -8376,7 +8385,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="292" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B292" s="8" t="s">
         <v>10</v>
       </c>
@@ -8402,7 +8411,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="293" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B293" s="8" t="s">
         <v>10</v>
       </c>
@@ -8428,7 +8437,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="294" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B294" s="8" t="s">
         <v>10</v>
       </c>
@@ -8454,7 +8463,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="295" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B295" s="8" t="s">
         <v>10</v>
       </c>
@@ -8480,7 +8489,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="296" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B296" s="8" t="s">
         <v>10</v>
       </c>
@@ -8506,7 +8515,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="297" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B297" s="8" t="s">
         <v>5</v>
       </c>
@@ -8532,7 +8541,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="298" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B298" s="8" t="s">
         <v>10</v>
       </c>
@@ -8558,7 +8567,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="299" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B299" s="8" t="s">
         <v>10</v>
       </c>
@@ -8584,7 +8593,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="300" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B300" s="8" t="s">
         <v>10</v>
       </c>
@@ -8610,7 +8619,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="301" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B301" s="8" t="s">
         <v>10</v>
       </c>
@@ -8636,7 +8645,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="302" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B302" s="8" t="s">
         <v>10</v>
       </c>
@@ -8662,7 +8671,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="303" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B303" s="8" t="s">
         <v>10</v>
       </c>
@@ -8688,7 +8697,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="304" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B304" s="8" t="s">
         <v>10</v>
       </c>
@@ -8714,7 +8723,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="305" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B305" s="8" t="s">
         <v>10</v>
       </c>
@@ -8740,7 +8749,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="306" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B306" s="8" t="s">
         <v>5</v>
       </c>
@@ -8766,7 +8775,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="307" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B307" s="8" t="s">
         <v>10</v>
       </c>
@@ -8792,7 +8801,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="308" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B308" s="8" t="s">
         <v>5</v>
       </c>
@@ -8818,7 +8827,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="309" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B309" s="8" t="s">
         <v>10</v>
       </c>
@@ -8844,7 +8853,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="310" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B310" s="8" t="s">
         <v>10</v>
       </c>
@@ -8870,7 +8879,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="311" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B311" s="8" t="s">
         <v>10</v>
       </c>
@@ -8896,7 +8905,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="312" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B312" s="8" t="s">
         <v>5</v>
       </c>
@@ -8922,7 +8931,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="313" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B313" s="8" t="s">
         <v>5</v>
       </c>
@@ -8948,7 +8957,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="314" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B314" s="8" t="s">
         <v>5</v>
       </c>
@@ -8974,7 +8983,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="315" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B315" s="8" t="s">
         <v>10</v>
       </c>
@@ -9000,7 +9009,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="316" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B316" s="8" t="s">
         <v>10</v>
       </c>
@@ -9026,7 +9035,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="317" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B317" s="8" t="s">
         <v>5</v>
       </c>
@@ -9052,7 +9061,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="318" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B318" s="8" t="s">
         <v>5</v>
       </c>
@@ -9078,7 +9087,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="319" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B319" s="8" t="s">
         <v>10</v>
       </c>
@@ -9104,7 +9113,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="320" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B320" s="8" t="s">
         <v>5</v>
       </c>
@@ -9130,7 +9139,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="321" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B321" s="8" t="s">
         <v>10</v>
       </c>
@@ -9156,7 +9165,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="322" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B322" s="8" t="s">
         <v>10</v>
       </c>
@@ -9182,7 +9191,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="323" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B323" s="8" t="s">
         <v>5</v>
       </c>
@@ -9208,7 +9217,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="324" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B324" s="8" t="s">
         <v>5</v>
       </c>
@@ -9234,7 +9243,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="325" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B325" s="8" t="s">
         <v>5</v>
       </c>
@@ -9260,7 +9269,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="326" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B326" s="8" t="s">
         <v>5</v>
       </c>
@@ -9286,7 +9295,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="327" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B327" s="8" t="s">
         <v>5</v>
       </c>
@@ -9312,7 +9321,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="328" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B328" s="8" t="s">
         <v>5</v>
       </c>
@@ -9338,7 +9347,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="329" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B329" s="8" t="s">
         <v>5</v>
       </c>
@@ -9364,7 +9373,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="330" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B330" s="8" t="s">
         <v>10</v>
       </c>
@@ -9390,7 +9399,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="331" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B331" s="8" t="s">
         <v>10</v>
       </c>
@@ -9416,7 +9425,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="332" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B332" s="8" t="s">
         <v>10</v>
       </c>
@@ -9442,7 +9451,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="333" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B333" s="8" t="s">
         <v>5</v>
       </c>
@@ -9468,7 +9477,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="334" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B334" s="8" t="s">
         <v>10</v>
       </c>
@@ -9494,7 +9503,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="335" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B335" s="8" t="s">
         <v>10</v>
       </c>
@@ -9520,7 +9529,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="336" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B336" s="8" t="s">
         <v>10</v>
       </c>
@@ -9546,7 +9555,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="337" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B337" s="8" t="s">
         <v>10</v>
       </c>
@@ -9572,7 +9581,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="338" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B338" s="8" t="s">
         <v>5</v>
       </c>
@@ -9598,7 +9607,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="339" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B339" s="8" t="s">
         <v>5</v>
       </c>
@@ -9624,7 +9633,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="340" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B340" s="8" t="s">
         <v>10</v>
       </c>
@@ -9650,7 +9659,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="341" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B341" s="8" t="s">
         <v>10</v>
       </c>
@@ -9676,7 +9685,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="342" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B342" s="8" t="s">
         <v>5</v>
       </c>
@@ -9702,7 +9711,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="343" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B343" s="8" t="s">
         <v>5</v>
       </c>
@@ -9728,7 +9737,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="344" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B344" s="8" t="s">
         <v>10</v>
       </c>
@@ -9754,7 +9763,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="345" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B345" s="8" t="s">
         <v>5</v>
       </c>
@@ -9780,7 +9789,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="346" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B346" s="8" t="s">
         <v>5</v>
       </c>
@@ -9806,7 +9815,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="347" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B347" s="8" t="s">
         <v>10</v>
       </c>
@@ -9832,7 +9841,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="348" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B348" s="8" t="s">
         <v>10</v>
       </c>
@@ -9858,7 +9867,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="349" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B349" s="8" t="s">
         <v>5</v>
       </c>
@@ -9884,7 +9893,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="350" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B350" s="8" t="s">
         <v>10</v>
       </c>
@@ -9910,7 +9919,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="351" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B351" s="8" t="s">
         <v>5</v>
       </c>
@@ -9936,7 +9945,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="352" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B352" s="8" t="s">
         <v>10</v>
       </c>
@@ -9962,7 +9971,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="353" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B353" s="8" t="s">
         <v>10</v>
       </c>
@@ -9988,7 +9997,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="354" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B354" s="8" t="s">
         <v>5</v>
       </c>
@@ -10014,7 +10023,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="355" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B355" s="8" t="s">
         <v>10</v>
       </c>
@@ -10040,7 +10049,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="356" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B356" s="8" t="s">
         <v>5</v>
       </c>
@@ -10066,7 +10075,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="357" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B357" s="8" t="s">
         <v>5</v>
       </c>
@@ -10092,7 +10101,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="358" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B358" s="8" t="s">
         <v>5</v>
       </c>
@@ -10118,7 +10127,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="359" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B359" s="8" t="s">
         <v>5</v>
       </c>
@@ -10144,7 +10153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="360" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B360" s="8" t="s">
         <v>10</v>
       </c>
@@ -10170,7 +10179,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="361" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B361" s="8" t="s">
         <v>5</v>
       </c>
@@ -10196,7 +10205,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="362" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B362" s="8" t="s">
         <v>10</v>
       </c>
@@ -10222,7 +10231,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="363" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B363" s="8" t="s">
         <v>5</v>
       </c>
@@ -10248,7 +10257,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="364" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B364" s="8" t="s">
         <v>5</v>
       </c>
@@ -10274,7 +10283,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="365" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B365" s="8" t="s">
         <v>10</v>
       </c>
@@ -10300,7 +10309,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="366" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B366" s="8" t="s">
         <v>5</v>
       </c>
@@ -10326,7 +10335,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="367" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B367" s="8" t="s">
         <v>5</v>
       </c>
@@ -10352,7 +10361,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="368" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B368" s="8" t="s">
         <v>10</v>
       </c>
@@ -10378,7 +10387,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="369" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B369" s="8" t="s">
         <v>10</v>
       </c>
@@ -10404,7 +10413,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="370" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B370" s="8" t="s">
         <v>10</v>
       </c>
@@ -10430,7 +10439,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="371" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B371" s="8" t="s">
         <v>10</v>
       </c>
@@ -10456,7 +10465,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="372" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B372" s="8" t="s">
         <v>5</v>
       </c>
@@ -10482,7 +10491,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="373" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B373" s="8" t="s">
         <v>5</v>
       </c>
@@ -10508,7 +10517,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="374" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B374" s="8" t="s">
         <v>10</v>
       </c>
@@ -10534,7 +10543,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="375" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B375" s="8" t="s">
         <v>5</v>
       </c>
@@ -10560,7 +10569,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="376" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B376" s="8" t="s">
         <v>10</v>
       </c>
@@ -10586,7 +10595,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="377" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B377" s="8" t="s">
         <v>5</v>
       </c>
@@ -10612,7 +10621,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="378" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B378" s="8" t="s">
         <v>5</v>
       </c>
@@ -10638,7 +10647,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="379" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B379" s="8" t="s">
         <v>10</v>
       </c>
@@ -10664,7 +10673,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="380" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B380" s="8" t="s">
         <v>5</v>
       </c>
@@ -10690,7 +10699,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="381" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B381" s="8" t="s">
         <v>5</v>
       </c>
@@ -10716,7 +10725,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="382" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B382" s="8" t="s">
         <v>5</v>
       </c>
@@ -10742,7 +10751,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="383" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B383" s="8" t="s">
         <v>10</v>
       </c>
@@ -10768,7 +10777,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="384" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B384" s="8" t="s">
         <v>5</v>
       </c>
@@ -10794,7 +10803,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="385" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B385" s="8" t="s">
         <v>10</v>
       </c>
@@ -10820,7 +10829,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="386" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B386" s="8" t="s">
         <v>10</v>
       </c>
@@ -10846,7 +10855,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="387" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B387" s="8" t="s">
         <v>5</v>
       </c>
@@ -10872,7 +10881,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="388" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B388" s="8" t="s">
         <v>5</v>
       </c>
@@ -10898,7 +10907,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="389" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B389" s="8" t="s">
         <v>5</v>
       </c>
@@ -10924,7 +10933,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="390" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B390" s="8" t="s">
         <v>5</v>
       </c>
@@ -10950,7 +10959,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="391" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B391" s="8" t="s">
         <v>5</v>
       </c>
@@ -10976,7 +10985,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="392" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B392" s="8" t="s">
         <v>5</v>
       </c>
@@ -11002,7 +11011,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="393" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B393" s="8" t="s">
         <v>10</v>
       </c>
@@ -11028,7 +11037,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="394" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B394" s="8" t="s">
         <v>10</v>
       </c>
@@ -11054,7 +11063,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="395" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B395" s="8" t="s">
         <v>5</v>
       </c>
@@ -11080,7 +11089,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="396" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B396" s="8" t="s">
         <v>10</v>
       </c>
@@ -11106,7 +11115,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="397" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B397" s="8" t="s">
         <v>10</v>
       </c>
@@ -11132,7 +11141,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="398" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B398" s="8" t="s">
         <v>5</v>
       </c>
@@ -11158,7 +11167,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="399" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B399" s="8" t="s">
         <v>10</v>
       </c>
@@ -11184,7 +11193,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="400" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B400" s="8" t="s">
         <v>5</v>
       </c>
@@ -11210,7 +11219,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="401" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B401" s="8" t="s">
         <v>5</v>
       </c>
@@ -11236,7 +11245,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="402" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B402" s="8" t="s">
         <v>10</v>
       </c>
@@ -11262,7 +11271,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="403" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B403" s="8" t="s">
         <v>10</v>
       </c>
@@ -11288,7 +11297,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="404" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B404" s="8" t="s">
         <v>5</v>
       </c>
@@ -11314,7 +11323,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="405" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B405" s="8" t="s">
         <v>10</v>
       </c>
@@ -11340,7 +11349,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="406" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B406" s="8" t="s">
         <v>5</v>
       </c>
@@ -11366,7 +11375,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="407" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B407" s="8" t="s">
         <v>5</v>
       </c>
@@ -11392,7 +11401,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="408" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B408" s="8" t="s">
         <v>5</v>
       </c>
@@ -11418,7 +11427,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="409" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B409" s="8" t="s">
         <v>5</v>
       </c>
@@ -11444,7 +11453,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="410" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B410" s="8" t="s">
         <v>10</v>
       </c>
@@ -11470,7 +11479,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="411" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B411" s="8" t="s">
         <v>5</v>
       </c>
@@ -11496,7 +11505,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="412" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B412" s="8" t="s">
         <v>5</v>
       </c>
@@ -11522,7 +11531,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="413" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B413" s="8" t="s">
         <v>10</v>
       </c>
@@ -11548,7 +11557,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="414" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B414" s="8" t="s">
         <v>5</v>
       </c>
@@ -11574,7 +11583,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="415" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B415" s="8" t="s">
         <v>10</v>
       </c>
@@ -11600,7 +11609,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="416" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B416" s="8" t="s">
         <v>10</v>
       </c>
@@ -11626,7 +11635,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="417" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B417" s="8" t="s">
         <v>10</v>
       </c>
@@ -11652,7 +11661,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="418" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B418" s="8" t="s">
         <v>5</v>
       </c>
@@ -11678,7 +11687,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="419" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B419" s="8" t="s">
         <v>10</v>
       </c>
@@ -11704,7 +11713,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="420" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B420" s="8" t="s">
         <v>10</v>
       </c>
@@ -11730,7 +11739,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="421" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B421" s="8" t="s">
         <v>10</v>
       </c>
@@ -11756,7 +11765,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="422" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B422" s="8" t="s">
         <v>10</v>
       </c>
@@ -11782,7 +11791,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="423" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B423" s="8" t="s">
         <v>10</v>
       </c>
@@ -11808,7 +11817,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="424" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B424" s="8" t="s">
         <v>5</v>
       </c>
@@ -11834,7 +11843,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="425" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B425" s="8" t="s">
         <v>5</v>
       </c>
@@ -11860,7 +11869,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="426" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B426" s="8" t="s">
         <v>5</v>
       </c>
@@ -11886,7 +11895,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="427" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B427" s="8" t="s">
         <v>5</v>
       </c>
@@ -11912,7 +11921,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="428" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B428" s="8" t="s">
         <v>10</v>
       </c>
@@ -11938,7 +11947,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="429" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B429" s="8" t="s">
         <v>5</v>
       </c>
@@ -11964,7 +11973,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="430" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B430" s="8" t="s">
         <v>10</v>
       </c>
@@ -11990,7 +11999,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="431" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B431" s="8" t="s">
         <v>10</v>
       </c>
@@ -12016,7 +12025,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="432" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B432" s="8" t="s">
         <v>10</v>
       </c>
@@ -12042,7 +12051,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="433" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B433" s="8" t="s">
         <v>10</v>
       </c>
@@ -12068,7 +12077,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="434" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B434" s="8" t="s">
         <v>10</v>
       </c>
@@ -12094,7 +12103,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="435" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B435" s="8" t="s">
         <v>5</v>
       </c>
@@ -12120,7 +12129,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="436" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B436" s="8" t="s">
         <v>10</v>
       </c>
@@ -12146,7 +12155,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="437" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B437" s="8" t="s">
         <v>5</v>
       </c>
@@ -12172,7 +12181,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="438" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B438" s="8" t="s">
         <v>10</v>
       </c>
@@ -12198,7 +12207,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="439" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B439" s="8" t="s">
         <v>10</v>
       </c>
@@ -12224,7 +12233,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="440" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B440" s="8" t="s">
         <v>10</v>
       </c>
@@ -12250,7 +12259,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="441" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B441" s="8" t="s">
         <v>10</v>
       </c>
@@ -12276,7 +12285,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="442" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B442" s="8" t="s">
         <v>10</v>
       </c>
@@ -12302,7 +12311,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="443" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B443" s="8" t="s">
         <v>10</v>
       </c>
@@ -12328,7 +12337,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="444" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B444" s="8" t="s">
         <v>5</v>
       </c>
@@ -12354,7 +12363,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="445" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B445" s="8" t="s">
         <v>5</v>
       </c>
@@ -12380,7 +12389,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="446" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B446" s="8" t="s">
         <v>5</v>
       </c>
@@ -12406,7 +12415,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="447" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B447" s="8" t="s">
         <v>5</v>
       </c>
@@ -12432,7 +12441,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="448" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B448" s="8" t="s">
         <v>10</v>
       </c>
@@ -12458,7 +12467,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="449" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B449" s="8" t="s">
         <v>5</v>
       </c>
@@ -12484,7 +12493,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="450" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B450" s="8" t="s">
         <v>10</v>
       </c>
@@ -12510,7 +12519,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="451" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B451" s="8" t="s">
         <v>10</v>
       </c>
@@ -12536,7 +12545,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="452" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B452" s="8" t="s">
         <v>10</v>
       </c>
@@ -12562,7 +12571,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="453" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B453" s="8" t="s">
         <v>10</v>
       </c>
@@ -12588,7 +12597,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="454" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B454" s="8" t="s">
         <v>5</v>
       </c>
@@ -12614,7 +12623,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="455" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B455" s="8" t="s">
         <v>5</v>
       </c>
@@ -12640,7 +12649,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="456" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B456" s="8" t="s">
         <v>5</v>
       </c>
@@ -12666,7 +12675,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="457" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B457" s="8" t="s">
         <v>10</v>
       </c>
@@ -12692,7 +12701,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="458" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B458" s="8" t="s">
         <v>5</v>
       </c>
@@ -12718,7 +12727,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="459" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B459" s="8" t="s">
         <v>10</v>
       </c>
@@ -12744,7 +12753,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="460" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B460" s="8" t="s">
         <v>5</v>
       </c>
@@ -12770,7 +12779,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="461" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B461" s="8" t="s">
         <v>10</v>
       </c>
@@ -12796,7 +12805,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="462" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B462" s="8" t="s">
         <v>5</v>
       </c>
@@ -12822,7 +12831,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="463" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B463" s="8" t="s">
         <v>10</v>
       </c>
@@ -12848,7 +12857,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="464" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B464" s="8" t="s">
         <v>10</v>
       </c>
@@ -12874,7 +12883,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="465" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B465" s="8" t="s">
         <v>10</v>
       </c>
@@ -12900,7 +12909,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="466" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B466" s="8" t="s">
         <v>5</v>
       </c>
@@ -12926,7 +12935,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="467" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B467" s="8" t="s">
         <v>5</v>
       </c>
@@ -12952,7 +12961,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="468" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B468" s="8" t="s">
         <v>10</v>
       </c>
@@ -12978,7 +12987,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="469" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B469" s="8" t="s">
         <v>5</v>
       </c>
@@ -13004,7 +13013,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="470" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B470" s="8" t="s">
         <v>5</v>
       </c>
@@ -13030,7 +13039,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="471" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B471" s="8" t="s">
         <v>10</v>
       </c>
@@ -13056,7 +13065,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="472" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B472" s="8" t="s">
         <v>5</v>
       </c>
@@ -13082,7 +13091,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="473" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B473" s="8" t="s">
         <v>10</v>
       </c>
@@ -13108,7 +13117,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="474" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B474" s="8" t="s">
         <v>5</v>
       </c>
@@ -13134,7 +13143,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="475" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B475" s="8" t="s">
         <v>5</v>
       </c>
@@ -13160,7 +13169,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="476" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B476" s="8" t="s">
         <v>5</v>
       </c>
@@ -13186,7 +13195,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="477" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B477" s="8" t="s">
         <v>5</v>
       </c>
@@ -13212,7 +13221,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="478" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B478" s="8" t="s">
         <v>5</v>
       </c>
@@ -13238,7 +13247,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="479" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B479" s="8" t="s">
         <v>5</v>
       </c>
@@ -13264,7 +13273,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="480" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B480" s="8" t="s">
         <v>10</v>
       </c>
@@ -13290,7 +13299,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="481" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B481" s="8" t="s">
         <v>10</v>
       </c>
@@ -13316,7 +13325,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="482" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B482" s="8" t="s">
         <v>5</v>
       </c>
@@ -13342,7 +13351,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="483" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B483" s="8" t="s">
         <v>10</v>
       </c>
@@ -13368,7 +13377,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="484" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B484" s="8" t="s">
         <v>10</v>
       </c>
@@ -13394,7 +13403,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="485" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B485" s="8" t="s">
         <v>5</v>
       </c>
@@ -13420,7 +13429,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="486" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B486" s="8" t="s">
         <v>10</v>
       </c>
@@ -13446,7 +13455,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="487" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B487" s="8" t="s">
         <v>10</v>
       </c>
@@ -13472,7 +13481,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="488" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B488" s="8" t="s">
         <v>5</v>
       </c>
@@ -13498,7 +13507,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="489" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B489" s="8" t="s">
         <v>10</v>
       </c>
@@ -13524,7 +13533,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="490" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B490" s="8" t="s">
         <v>10</v>
       </c>
@@ -13550,7 +13559,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="491" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B491" s="8" t="s">
         <v>5</v>
       </c>
@@ -13576,7 +13585,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="492" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B492" s="8" t="s">
         <v>10</v>
       </c>
@@ -13602,7 +13611,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="493" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B493" s="8" t="s">
         <v>10</v>
       </c>
@@ -13628,7 +13637,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="494" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B494" s="8" t="s">
         <v>5</v>
       </c>
@@ -13654,7 +13663,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="495" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B495" s="8" t="s">
         <v>5</v>
       </c>
@@ -13680,7 +13689,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="496" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B496" s="8" t="s">
         <v>5</v>
       </c>
@@ -13706,7 +13715,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="497" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B497" s="8" t="s">
         <v>5</v>
       </c>
@@ -13732,7 +13741,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="498" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B498" s="8" t="s">
         <v>5</v>
       </c>
@@ -13758,7 +13767,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="499" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B499" s="8" t="s">
         <v>10</v>
       </c>
@@ -13784,7 +13793,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="500" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B500" s="8" t="s">
         <v>5</v>
       </c>
@@ -13810,7 +13819,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="501" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B501" s="8" t="s">
         <v>5</v>
       </c>
@@ -13836,7 +13845,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="502" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B502" s="8" t="s">
         <v>5</v>
       </c>
@@ -13862,7 +13871,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="503" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B503" s="8" t="s">
         <v>10</v>
       </c>
@@ -13888,7 +13897,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="504" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B504" s="8" t="s">
         <v>5</v>
       </c>
@@ -13914,7 +13923,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="505" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B505" s="8" t="s">
         <v>5</v>
       </c>
@@ -13940,7 +13949,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="506" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B506" s="8" t="s">
         <v>10</v>
       </c>
@@ -13966,7 +13975,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="507" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B507" s="8" t="s">
         <v>5</v>
       </c>
@@ -13992,7 +14001,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="508" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B508" s="8" t="s">
         <v>5</v>
       </c>
@@ -14018,7 +14027,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="509" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B509" s="8" t="s">
         <v>5</v>
       </c>
@@ -14044,7 +14053,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="510" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B510" s="8" t="s">
         <v>10</v>
       </c>
@@ -14070,7 +14079,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="511" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B511" s="8" t="s">
         <v>10</v>
       </c>
@@ -14096,7 +14105,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="512" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B512" s="8" t="s">
         <v>10</v>
       </c>
@@ -14122,7 +14131,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="513" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B513" s="8" t="s">
         <v>5</v>
       </c>
@@ -14148,7 +14157,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="514" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B514" s="8" t="s">
         <v>10</v>
       </c>
@@ -14174,7 +14183,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="515" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B515" s="8" t="s">
         <v>10</v>
       </c>
@@ -14200,7 +14209,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="516" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B516" s="8" t="s">
         <v>10</v>
       </c>
@@ -14226,7 +14235,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="517" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B517" s="8" t="s">
         <v>5</v>
       </c>
@@ -14252,7 +14261,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="518" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B518" s="8" t="s">
         <v>5</v>
       </c>
@@ -14278,7 +14287,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="519" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B519" s="8" t="s">
         <v>5</v>
       </c>
@@ -14304,7 +14313,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="520" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B520" s="8" t="s">
         <v>5</v>
       </c>
@@ -14330,7 +14339,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="521" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B521" s="8" t="s">
         <v>5</v>
       </c>
@@ -14356,7 +14365,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="522" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B522" s="8" t="s">
         <v>5</v>
       </c>
@@ -14382,7 +14391,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="523" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B523" s="8" t="s">
         <v>5</v>
       </c>
@@ -14408,7 +14417,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="524" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B524" s="8" t="s">
         <v>10</v>
       </c>
@@ -14434,7 +14443,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="525" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B525" s="8" t="s">
         <v>5</v>
       </c>
@@ -14460,7 +14469,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="526" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B526" s="8" t="s">
         <v>10</v>
       </c>
@@ -14486,7 +14495,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="527" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B527" s="8" t="s">
         <v>10</v>
       </c>
@@ -14512,7 +14521,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="528" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B528" s="8" t="s">
         <v>10</v>
       </c>
@@ -14538,7 +14547,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="529" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B529" s="8" t="s">
         <v>10</v>
       </c>
@@ -14564,7 +14573,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="530" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B530" s="8" t="s">
         <v>10</v>
       </c>
@@ -14590,7 +14599,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="531" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B531" s="8" t="s">
         <v>5</v>
       </c>
@@ -14616,7 +14625,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="532" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B532" s="8" t="s">
         <v>5</v>
       </c>
@@ -14642,7 +14651,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="533" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B533" s="8" t="s">
         <v>5</v>
       </c>
@@ -14668,7 +14677,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="534" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B534" s="8" t="s">
         <v>5</v>
       </c>
@@ -14694,7 +14703,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="535" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B535" s="8" t="s">
         <v>5</v>
       </c>
@@ -14720,7 +14729,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="536" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B536" s="8" t="s">
         <v>10</v>
       </c>
@@ -14746,7 +14755,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="537" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B537" s="8" t="s">
         <v>5</v>
       </c>
@@ -14772,7 +14781,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="538" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B538" s="8" t="s">
         <v>10</v>
       </c>
@@ -14798,7 +14807,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="539" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B539" s="8" t="s">
         <v>5</v>
       </c>
@@ -14824,7 +14833,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="540" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B540" s="8" t="s">
         <v>10</v>
       </c>
@@ -14850,7 +14859,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="541" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B541" s="8" t="s">
         <v>5</v>
       </c>
@@ -14876,7 +14885,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="542" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B542" s="8" t="s">
         <v>10</v>
       </c>
@@ -14902,7 +14911,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="543" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B543" s="8" t="s">
         <v>10</v>
       </c>
@@ -14928,7 +14937,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="544" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B544" s="8" t="s">
         <v>10</v>
       </c>
@@ -14954,7 +14963,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="545" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B545" s="8" t="s">
         <v>10</v>
       </c>
@@ -14980,7 +14989,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="546" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B546" s="8" t="s">
         <v>5</v>
       </c>
@@ -15006,7 +15015,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="547" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B547" s="8" t="s">
         <v>5</v>
       </c>
@@ -15032,7 +15041,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="548" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B548" s="8" t="s">
         <v>5</v>
       </c>
@@ -15058,7 +15067,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="549" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B549" s="8" t="s">
         <v>10</v>
       </c>
@@ -15084,7 +15093,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="550" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B550" s="8" t="s">
         <v>5</v>
       </c>
@@ -15110,7 +15119,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="551" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B551" s="8" t="s">
         <v>10</v>
       </c>
@@ -15136,7 +15145,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="552" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B552" s="8" t="s">
         <v>5</v>
       </c>
@@ -15162,7 +15171,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="553" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B553" s="8" t="s">
         <v>10</v>
       </c>
@@ -15188,7 +15197,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="554" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B554" s="8" t="s">
         <v>10</v>
       </c>
@@ -15214,7 +15223,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="555" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B555" s="8" t="s">
         <v>10</v>
       </c>
@@ -15240,7 +15249,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="556" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B556" s="8" t="s">
         <v>5</v>
       </c>
@@ -15266,7 +15275,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="557" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B557" s="8" t="s">
         <v>10</v>
       </c>
@@ -15292,7 +15301,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="558" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B558" s="8" t="s">
         <v>10</v>
       </c>
@@ -15318,7 +15327,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="559" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B559" s="8" t="s">
         <v>5</v>
       </c>
@@ -15344,7 +15353,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="560" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B560" s="8" t="s">
         <v>5</v>
       </c>
@@ -15370,7 +15379,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="561" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B561" s="8" t="s">
         <v>10</v>
       </c>
@@ -15396,7 +15405,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="562" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B562" s="8" t="s">
         <v>5</v>
       </c>
@@ -15422,7 +15431,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="563" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B563" s="8" t="s">
         <v>10</v>
       </c>
@@ -15448,7 +15457,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="564" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B564" s="8" t="s">
         <v>5</v>
       </c>
@@ -15474,7 +15483,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="565" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B565" s="8" t="s">
         <v>5</v>
       </c>
@@ -15500,7 +15509,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="566" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B566" s="8" t="s">
         <v>10</v>
       </c>
@@ -15526,7 +15535,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="567" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B567" s="8" t="s">
         <v>5</v>
       </c>
@@ -15552,7 +15561,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="568" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B568" s="8" t="s">
         <v>10</v>
       </c>
@@ -15578,7 +15587,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="569" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B569" s="8" t="s">
         <v>10</v>
       </c>
@@ -15604,7 +15613,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="570" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B570" s="8" t="s">
         <v>5</v>
       </c>
@@ -15630,7 +15639,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="571" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B571" s="8" t="s">
         <v>5</v>
       </c>
@@ -15656,7 +15665,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="572" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B572" s="8" t="s">
         <v>10</v>
       </c>
@@ -15682,7 +15691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="573" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B573" s="8" t="s">
         <v>10</v>
       </c>
@@ -15708,7 +15717,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="574" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B574" s="8" t="s">
         <v>10</v>
       </c>
@@ -15734,7 +15743,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="575" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B575" s="8" t="s">
         <v>10</v>
       </c>
@@ -15760,7 +15769,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="576" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B576" s="8" t="s">
         <v>5</v>
       </c>
@@ -15786,7 +15795,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="577" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B577" s="8" t="s">
         <v>5</v>
       </c>
@@ -15812,7 +15821,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="578" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B578" s="8" t="s">
         <v>5</v>
       </c>
@@ -15838,7 +15847,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="579" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B579" s="8" t="s">
         <v>10</v>
       </c>
@@ -15864,7 +15873,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="580" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B580" s="8" t="s">
         <v>10</v>
       </c>
@@ -15890,7 +15899,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="581" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="581" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B581" s="8" t="s">
         <v>5</v>
       </c>
@@ -15916,7 +15925,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="582" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="582" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B582" s="8" t="s">
         <v>5</v>
       </c>
@@ -15942,7 +15951,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="583" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B583" s="8" t="s">
         <v>5</v>
       </c>
@@ -15968,7 +15977,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="584" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B584" s="8" t="s">
         <v>5</v>
       </c>
@@ -15994,7 +16003,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="585" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B585" s="8" t="s">
         <v>5</v>
       </c>
@@ -16020,7 +16029,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="586" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B586" s="8" t="s">
         <v>5</v>
       </c>
@@ -16046,7 +16055,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="587" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B587" s="8" t="s">
         <v>5</v>
       </c>
@@ -16072,7 +16081,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="588" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B588" s="8" t="s">
         <v>5</v>
       </c>
@@ -16098,7 +16107,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="589" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B589" s="8" t="s">
         <v>5</v>
       </c>
@@ -16124,7 +16133,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="590" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B590" s="8" t="s">
         <v>5</v>
       </c>
@@ -16150,7 +16159,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="591" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B591" s="8" t="s">
         <v>5</v>
       </c>
@@ -16176,7 +16185,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="592" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B592" s="8" t="s">
         <v>5</v>
       </c>
@@ -16202,7 +16211,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="593" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="593" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B593" s="8" t="s">
         <v>5</v>
       </c>
@@ -16228,7 +16237,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="594" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B594" s="8" t="s">
         <v>10</v>
       </c>
@@ -16254,7 +16263,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="595" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B595" s="8" t="s">
         <v>10</v>
       </c>
@@ -16280,7 +16289,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="596" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B596" s="8" t="s">
         <v>10</v>
       </c>
@@ -16306,7 +16315,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="597" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B597" s="8" t="s">
         <v>5</v>
       </c>
@@ -16332,7 +16341,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="598" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="598" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B598" s="8" t="s">
         <v>5</v>
       </c>
@@ -16358,7 +16367,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="599" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="599" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B599" s="8" t="s">
         <v>5</v>
       </c>
@@ -16384,7 +16393,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="600" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="600" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B600" s="8" t="s">
         <v>10</v>
       </c>
@@ -16410,7 +16419,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="601" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B601" s="8" t="s">
         <v>10</v>
       </c>
@@ -16436,7 +16445,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="602" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B602" s="8" t="s">
         <v>5</v>
       </c>
@@ -16462,7 +16471,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="603" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B603" s="8" t="s">
         <v>5</v>
       </c>
@@ -16488,7 +16497,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="604" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B604" s="8" t="s">
         <v>5</v>
       </c>
@@ -16514,7 +16523,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="605" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B605" s="8" t="s">
         <v>5</v>
       </c>
@@ -16540,7 +16549,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="606" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B606" s="8" t="s">
         <v>5</v>
       </c>
@@ -16566,7 +16575,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="607" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="607" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B607" s="8" t="s">
         <v>10</v>
       </c>
@@ -16592,7 +16601,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="608" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B608" s="8" t="s">
         <v>10</v>
       </c>
@@ -16618,7 +16627,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="609" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B609" s="8" t="s">
         <v>10</v>
       </c>
@@ -16644,7 +16653,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="610" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B610" s="8" t="s">
         <v>5</v>
       </c>
@@ -16670,7 +16679,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="611" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B611" s="8" t="s">
         <v>5</v>
       </c>
@@ -16696,7 +16705,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="612" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="612" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B612" s="8" t="s">
         <v>5</v>
       </c>
@@ -16722,7 +16731,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="613" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="613" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B613" s="8" t="s">
         <v>5</v>
       </c>
@@ -16748,7 +16757,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="614" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B614" s="8" t="s">
         <v>10</v>
       </c>
@@ -16774,7 +16783,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="615" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="615" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B615" s="8" t="s">
         <v>5</v>
       </c>
@@ -16800,7 +16809,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="616" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B616" s="8" t="s">
         <v>10</v>
       </c>
@@ -16826,7 +16835,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="617" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B617" s="8" t="s">
         <v>5</v>
       </c>
@@ -16852,7 +16861,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="618" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="618" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B618" s="8" t="s">
         <v>5</v>
       </c>
@@ -16878,7 +16887,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="619" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="619" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B619" s="8" t="s">
         <v>5</v>
       </c>
@@ -16904,7 +16913,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="620" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="620" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B620" s="8" t="s">
         <v>5</v>
       </c>
@@ -16930,7 +16939,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="621" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="621" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B621" s="8" t="s">
         <v>10</v>
       </c>
@@ -16956,7 +16965,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="622" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B622" s="8" t="s">
         <v>10</v>
       </c>
@@ -16982,7 +16991,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="623" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B623" s="8" t="s">
         <v>10</v>
       </c>
@@ -17008,7 +17017,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="624" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B624" s="8" t="s">
         <v>5</v>
       </c>
@@ -17034,7 +17043,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="625" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="625" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B625" s="8" t="s">
         <v>10</v>
       </c>
@@ -17060,7 +17069,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="626" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="626" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B626" s="8" t="s">
         <v>10</v>
       </c>
@@ -17086,7 +17095,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="627" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="627" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B627" s="8" t="s">
         <v>10</v>
       </c>
@@ -17112,7 +17121,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="628" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="628" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B628" s="8" t="s">
         <v>5</v>
       </c>
@@ -17138,7 +17147,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="629" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="629" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B629" s="8" t="s">
         <v>10</v>
       </c>
@@ -17164,7 +17173,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="630" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="630" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B630" s="8" t="s">
         <v>10</v>
       </c>
@@ -17190,7 +17199,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="631" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="631" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B631" s="8" t="s">
         <v>10</v>
       </c>
@@ -17216,7 +17225,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="632" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="632" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B632" s="8" t="s">
         <v>10</v>
       </c>
@@ -17242,7 +17251,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="633" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="633" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B633" s="8" t="s">
         <v>5</v>
       </c>
@@ -17268,7 +17277,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="634" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B634" s="8" t="s">
         <v>10</v>
       </c>
@@ -17294,7 +17303,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="635" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="635" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B635" s="8" t="s">
         <v>10</v>
       </c>
@@ -17320,7 +17329,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="636" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="636" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B636" s="8" t="s">
         <v>5</v>
       </c>
@@ -17346,7 +17355,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="637" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B637" s="8" t="s">
         <v>5</v>
       </c>
@@ -17372,7 +17381,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="638" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B638" s="8" t="s">
         <v>10</v>
       </c>
@@ -17398,7 +17407,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="639" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B639" s="8" t="s">
         <v>10</v>
       </c>
@@ -17424,7 +17433,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="640" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B640" s="8" t="s">
         <v>5</v>
       </c>
@@ -17450,7 +17459,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="641" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="641" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B641" s="8" t="s">
         <v>5</v>
       </c>
@@ -17476,7 +17485,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="642" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="642" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B642" s="8" t="s">
         <v>10</v>
       </c>
@@ -17502,7 +17511,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="643" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="643" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B643" s="8" t="s">
         <v>5</v>
       </c>
@@ -17528,7 +17537,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="644" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="644" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B644" s="8" t="s">
         <v>10</v>
       </c>
@@ -17554,7 +17563,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="645" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="645" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B645" s="8" t="s">
         <v>5</v>
       </c>
@@ -17580,7 +17589,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="646" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="646" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B646" s="8" t="s">
         <v>5</v>
       </c>
@@ -17606,7 +17615,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="647" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="647" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B647" s="8" t="s">
         <v>5</v>
       </c>
@@ -17632,7 +17641,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="648" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="648" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B648" s="8" t="s">
         <v>10</v>
       </c>
@@ -17658,7 +17667,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="649" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="649" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B649" s="8" t="s">
         <v>5</v>
       </c>
@@ -17684,7 +17693,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="650" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="650" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B650" s="8" t="s">
         <v>5</v>
       </c>
@@ -17710,7 +17719,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="651" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="651" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B651" s="8" t="s">
         <v>5</v>
       </c>
@@ -17736,7 +17745,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="652" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="652" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B652" s="8" t="s">
         <v>5</v>
       </c>
@@ -17762,7 +17771,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="653" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="653" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B653" s="8" t="s">
         <v>5</v>
       </c>
@@ -17788,7 +17797,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="654" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="654" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B654" s="8" t="s">
         <v>10</v>
       </c>
@@ -17814,7 +17823,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="655" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="655" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B655" s="8" t="s">
         <v>5</v>
       </c>
@@ -17840,7 +17849,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="656" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="656" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B656" s="8" t="s">
         <v>5</v>
       </c>
@@ -17866,7 +17875,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="657" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="657" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B657" s="8" t="s">
         <v>5</v>
       </c>
@@ -17892,7 +17901,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="658" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="658" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B658" s="8" t="s">
         <v>5</v>
       </c>
@@ -17918,7 +17927,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="659" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="659" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B659" s="8" t="s">
         <v>5</v>
       </c>
@@ -17944,7 +17953,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="660" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="660" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B660" s="8" t="s">
         <v>10</v>
       </c>
@@ -17970,7 +17979,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="661" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="661" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B661" s="8" t="s">
         <v>10</v>
       </c>
@@ -17996,7 +18005,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="662" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="662" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B662" s="8" t="s">
         <v>5</v>
       </c>
@@ -18022,7 +18031,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="663" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="663" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B663" s="8" t="s">
         <v>10</v>
       </c>
@@ -18048,7 +18057,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="664" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="664" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B664" s="8" t="s">
         <v>10</v>
       </c>
@@ -18074,7 +18083,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="665" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="665" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B665" s="8" t="s">
         <v>10</v>
       </c>
@@ -18100,7 +18109,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="666" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="666" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B666" s="8" t="s">
         <v>5</v>
       </c>
@@ -18126,7 +18135,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="667" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="667" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B667" s="8" t="s">
         <v>5</v>
       </c>
@@ -18152,7 +18161,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="668" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="668" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B668" s="8" t="s">
         <v>10</v>
       </c>
@@ -18178,7 +18187,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="669" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="669" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B669" s="8" t="s">
         <v>5</v>
       </c>
@@ -18204,7 +18213,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="670" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="670" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B670" s="8" t="s">
         <v>5</v>
       </c>
@@ -18230,7 +18239,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="671" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="671" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B671" s="8" t="s">
         <v>5</v>
       </c>
@@ -18256,7 +18265,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="672" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="672" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B672" s="8" t="s">
         <v>10</v>
       </c>
@@ -18282,7 +18291,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="673" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="673" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B673" s="8" t="s">
         <v>10</v>
       </c>
@@ -18308,7 +18317,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="674" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="674" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B674" s="8" t="s">
         <v>5</v>
       </c>
@@ -18334,7 +18343,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="675" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="675" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B675" s="8" t="s">
         <v>10</v>
       </c>
@@ -18360,7 +18369,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="676" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="676" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B676" s="8" t="s">
         <v>5</v>
       </c>
@@ -18386,7 +18395,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="677" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="677" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B677" s="8" t="s">
         <v>5</v>
       </c>
@@ -18412,7 +18421,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="678" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="678" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B678" s="8" t="s">
         <v>5</v>
       </c>
@@ -18438,7 +18447,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="679" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="679" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B679" s="8" t="s">
         <v>5</v>
       </c>
@@ -18464,7 +18473,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="680" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="680" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B680" s="8" t="s">
         <v>5</v>
       </c>
@@ -18490,7 +18499,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="681" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="681" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B681" s="8" t="s">
         <v>5</v>
       </c>
@@ -18516,7 +18525,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="682" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="682" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B682" s="8" t="s">
         <v>10</v>
       </c>
@@ -18542,7 +18551,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="683" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="683" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B683" s="8" t="s">
         <v>10</v>
       </c>
@@ -18568,7 +18577,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="684" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="684" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B684" s="8" t="s">
         <v>5</v>
       </c>
@@ -18594,7 +18603,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="685" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="685" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B685" s="8" t="s">
         <v>10</v>
       </c>
@@ -18620,7 +18629,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="686" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="686" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B686" s="8" t="s">
         <v>10</v>
       </c>
@@ -18646,7 +18655,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="687" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="687" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B687" s="8" t="s">
         <v>5</v>
       </c>
@@ -18672,7 +18681,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="688" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="688" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B688" s="8" t="s">
         <v>10</v>
       </c>
@@ -18698,7 +18707,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="689" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="689" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B689" s="8" t="s">
         <v>5</v>
       </c>
@@ -18724,7 +18733,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="690" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="690" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B690" s="8" t="s">
         <v>10</v>
       </c>
@@ -18750,7 +18759,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="691" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="691" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B691" s="8" t="s">
         <v>10</v>
       </c>
@@ -18776,7 +18785,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="692" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="692" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B692" s="8" t="s">
         <v>10</v>
       </c>
@@ -18802,7 +18811,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="693" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="693" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B693" s="8" t="s">
         <v>10</v>
       </c>
@@ -18828,7 +18837,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="694" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="694" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B694" s="8" t="s">
         <v>5</v>
       </c>
@@ -18854,7 +18863,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="695" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="695" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B695" s="8" t="s">
         <v>5</v>
       </c>
@@ -18880,7 +18889,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="696" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="696" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B696" s="8" t="s">
         <v>5</v>
       </c>
@@ -18906,7 +18915,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="697" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="697" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B697" s="8" t="s">
         <v>5</v>
       </c>
@@ -18932,7 +18941,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="698" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="698" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B698" s="8" t="s">
         <v>5</v>
       </c>
@@ -18958,7 +18967,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="699" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="699" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B699" s="8" t="s">
         <v>5</v>
       </c>
@@ -18984,7 +18993,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="700" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="700" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B700" s="8" t="s">
         <v>5</v>
       </c>
@@ -19010,7 +19019,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="701" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="701" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B701" s="8" t="s">
         <v>5</v>
       </c>
@@ -19036,7 +19045,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="702" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B702" s="8" t="s">
         <v>5</v>
       </c>
@@ -19062,7 +19071,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="703" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="703" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B703" s="8" t="s">
         <v>10</v>
       </c>
@@ -19088,7 +19097,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="704" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="704" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B704" s="8" t="s">
         <v>5</v>
       </c>
@@ -19114,7 +19123,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="705" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="705" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B705" s="8" t="s">
         <v>5</v>
       </c>
@@ -19140,7 +19149,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="706" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B706" s="8" t="s">
         <v>10</v>
       </c>
@@ -19166,7 +19175,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="707" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B707" s="8" t="s">
         <v>5</v>
       </c>
@@ -19192,7 +19201,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="708" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B708" s="8" t="s">
         <v>5</v>
       </c>
@@ -19218,7 +19227,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="709" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="709" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B709" s="8" t="s">
         <v>10</v>
       </c>
@@ -19244,7 +19253,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="710" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B710" s="8" t="s">
         <v>10</v>
       </c>
@@ -19270,7 +19279,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="711" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B711" s="8" t="s">
         <v>10</v>
       </c>
@@ -19296,7 +19305,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="712" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B712" s="8" t="s">
         <v>10</v>
       </c>
@@ -19322,7 +19331,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="713" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="713" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B713" s="8" t="s">
         <v>5</v>
       </c>
@@ -19348,7 +19357,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="714" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="714" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B714" s="8" t="s">
         <v>10</v>
       </c>
@@ -19374,7 +19383,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="715" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="715" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B715" s="8" t="s">
         <v>5</v>
       </c>
@@ -19400,7 +19409,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="716" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="716" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B716" s="8" t="s">
         <v>5</v>
       </c>
@@ -19426,7 +19435,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="717" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="717" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B717" s="8" t="s">
         <v>10</v>
       </c>
@@ -19452,7 +19461,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="718" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="718" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B718" s="8" t="s">
         <v>5</v>
       </c>
@@ -19478,7 +19487,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="719" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="719" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B719" s="8" t="s">
         <v>5</v>
       </c>
@@ -19504,7 +19513,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="720" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="720" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B720" s="8" t="s">
         <v>10</v>
       </c>
@@ -19530,7 +19539,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="721" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="721" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B721" s="8" t="s">
         <v>5</v>
       </c>
@@ -19556,7 +19565,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="722" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="722" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B722" s="8" t="s">
         <v>5</v>
       </c>
@@ -19582,7 +19591,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="723" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="723" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B723" s="8" t="s">
         <v>10</v>
       </c>
@@ -19608,7 +19617,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="724" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="724" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B724" s="8" t="s">
         <v>5</v>
       </c>
@@ -19634,7 +19643,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="725" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="725" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B725" s="8" t="s">
         <v>10</v>
       </c>
@@ -19660,7 +19669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="726" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="726" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B726" s="8" t="s">
         <v>5</v>
       </c>
@@ -19686,7 +19695,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="727" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="727" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B727" s="8" t="s">
         <v>10</v>
       </c>
@@ -19712,7 +19721,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="728" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="728" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B728" s="8" t="s">
         <v>10</v>
       </c>
@@ -19738,7 +19747,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="729" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="729" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B729" s="8" t="s">
         <v>10</v>
       </c>
@@ -19764,7 +19773,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="730" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="730" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B730" s="8" t="s">
         <v>5</v>
       </c>
@@ -19790,7 +19799,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="731" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="731" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B731" s="8" t="s">
         <v>10</v>
       </c>
@@ -19816,7 +19825,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="732" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="732" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B732" s="8" t="s">
         <v>5</v>
       </c>
@@ -19842,7 +19851,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="733" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="733" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B733" s="8" t="s">
         <v>10</v>
       </c>
@@ -19868,7 +19877,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="734" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="734" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B734" s="8" t="s">
         <v>5</v>
       </c>
@@ -19894,7 +19903,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="735" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="735" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B735" s="8" t="s">
         <v>10</v>
       </c>
@@ -19920,7 +19929,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="736" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="736" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B736" s="8" t="s">
         <v>5</v>
       </c>
@@ -19946,7 +19955,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="737" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="737" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B737" s="8" t="s">
         <v>10</v>
       </c>
@@ -19972,7 +19981,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="738" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="738" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B738" s="8" t="s">
         <v>5</v>
       </c>
@@ -19998,7 +20007,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="739" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="739" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B739" s="8" t="s">
         <v>10</v>
       </c>
@@ -20024,7 +20033,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="740" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="740" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B740" s="8" t="s">
         <v>10</v>
       </c>
@@ -20050,7 +20059,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="741" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="741" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B741" s="8" t="s">
         <v>5</v>
       </c>
@@ -20076,7 +20085,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="742" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="742" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B742" s="8" t="s">
         <v>10</v>
       </c>
@@ -20102,7 +20111,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="743" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="743" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B743" s="8" t="s">
         <v>10</v>
       </c>
@@ -20128,7 +20137,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="744" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="744" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B744" s="8" t="s">
         <v>10</v>
       </c>
@@ -20154,7 +20163,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="745" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="745" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B745" s="8" t="s">
         <v>5</v>
       </c>
@@ -20180,7 +20189,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="746" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="746" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B746" s="8" t="s">
         <v>5</v>
       </c>
@@ -20206,7 +20215,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="747" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="747" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B747" s="8" t="s">
         <v>5</v>
       </c>
@@ -20232,7 +20241,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="748" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="748" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B748" s="8" t="s">
         <v>10</v>
       </c>
@@ -20258,7 +20267,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="749" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="749" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B749" s="8" t="s">
         <v>10</v>
       </c>
@@ -20284,7 +20293,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="750" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="750" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B750" s="8" t="s">
         <v>10</v>
       </c>
@@ -20310,7 +20319,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="751" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="751" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B751" s="8" t="s">
         <v>10</v>
       </c>
@@ -20336,7 +20345,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="752" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="752" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B752" s="8" t="s">
         <v>5</v>
       </c>
@@ -20362,7 +20371,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="753" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="753" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B753" s="8" t="s">
         <v>10</v>
       </c>
@@ -20388,7 +20397,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="754" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="754" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B754" s="8" t="s">
         <v>10</v>
       </c>
@@ -20414,7 +20423,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="755" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="755" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B755" s="8" t="s">
         <v>10</v>
       </c>
@@ -20440,7 +20449,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="756" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="756" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B756" s="8" t="s">
         <v>10</v>
       </c>
@@ -20466,7 +20475,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="757" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="757" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B757" s="8" t="s">
         <v>5</v>
       </c>
@@ -20492,7 +20501,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="758" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="758" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B758" s="8" t="s">
         <v>10</v>
       </c>
@@ -20518,7 +20527,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="759" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="759" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B759" s="8" t="s">
         <v>5</v>
       </c>
@@ -20544,7 +20553,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="760" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="760" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B760" s="8" t="s">
         <v>10</v>
       </c>
@@ -20570,7 +20579,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="761" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="761" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B761" s="8" t="s">
         <v>10</v>
       </c>
@@ -20596,7 +20605,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="762" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="762" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B762" s="8" t="s">
         <v>5</v>
       </c>
@@ -20622,7 +20631,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="763" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="763" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B763" s="8" t="s">
         <v>10</v>
       </c>
@@ -20648,7 +20657,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="764" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="764" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B764" s="8" t="s">
         <v>5</v>
       </c>
@@ -20674,7 +20683,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="765" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="765" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B765" s="8" t="s">
         <v>5</v>
       </c>
@@ -20700,7 +20709,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="766" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="766" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B766" s="8" t="s">
         <v>10</v>
       </c>
@@ -20726,7 +20735,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="767" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="767" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B767" s="8" t="s">
         <v>5</v>
       </c>
@@ -20752,7 +20761,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="768" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="768" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B768" s="8" t="s">
         <v>10</v>
       </c>
@@ -20778,7 +20787,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="769" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="769" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B769" s="8" t="s">
         <v>5</v>
       </c>
@@ -20804,7 +20813,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="770" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="770" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B770" s="8" t="s">
         <v>5</v>
       </c>
@@ -20830,7 +20839,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="771" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="771" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B771" s="8" t="s">
         <v>10</v>
       </c>
@@ -20856,7 +20865,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="772" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="772" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B772" s="8" t="s">
         <v>5</v>
       </c>
@@ -20882,7 +20891,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="773" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="773" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B773" s="8" t="s">
         <v>10</v>
       </c>
@@ -20908,7 +20917,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="774" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="774" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B774" s="8" t="s">
         <v>10</v>
       </c>
@@ -20934,7 +20943,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="775" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="775" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B775" s="8" t="s">
         <v>10</v>
       </c>
@@ -20960,7 +20969,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="776" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="776" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B776" s="8" t="s">
         <v>5</v>
       </c>
@@ -20986,7 +20995,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="777" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="777" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B777" s="8" t="s">
         <v>5</v>
       </c>
@@ -21012,7 +21021,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="778" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="778" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B778" s="8" t="s">
         <v>10</v>
       </c>
@@ -21038,7 +21047,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="779" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="779" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B779" s="8" t="s">
         <v>5</v>
       </c>
@@ -21064,7 +21073,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="780" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="780" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B780" s="8" t="s">
         <v>5</v>
       </c>
@@ -21090,7 +21099,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="781" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="781" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B781" s="8" t="s">
         <v>5</v>
       </c>
@@ -21116,7 +21125,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="782" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="782" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B782" s="8" t="s">
         <v>5</v>
       </c>
@@ -21142,7 +21151,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="783" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="783" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B783" s="8" t="s">
         <v>10</v>
       </c>
@@ -21168,7 +21177,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="784" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="784" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B784" s="8" t="s">
         <v>5</v>
       </c>
@@ -21194,7 +21203,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="785" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="785" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B785" s="8" t="s">
         <v>5</v>
       </c>
@@ -21220,7 +21229,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="786" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="786" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B786" s="8" t="s">
         <v>5</v>
       </c>
@@ -21246,7 +21255,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="787" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="787" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B787" s="8" t="s">
         <v>5</v>
       </c>
@@ -21272,7 +21281,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="788" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="788" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B788" s="8" t="s">
         <v>10</v>
       </c>
@@ -21298,7 +21307,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="789" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="789" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B789" s="8" t="s">
         <v>5</v>
       </c>
@@ -21324,7 +21333,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="790" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="790" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B790" s="8" t="s">
         <v>5</v>
       </c>
@@ -21350,7 +21359,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="791" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="791" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B791" s="8" t="s">
         <v>5</v>
       </c>
@@ -21376,7 +21385,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="792" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="792" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B792" s="8" t="s">
         <v>10</v>
       </c>
@@ -21402,7 +21411,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="793" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="793" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B793" s="8" t="s">
         <v>5</v>
       </c>
@@ -21428,7 +21437,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="794" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="794" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B794" s="8" t="s">
         <v>5</v>
       </c>
@@ -21454,7 +21463,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="795" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="795" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B795" s="8" t="s">
         <v>5</v>
       </c>
@@ -21480,7 +21489,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="796" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="796" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B796" s="8" t="s">
         <v>10</v>
       </c>
@@ -21506,7 +21515,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="797" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="797" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B797" s="8" t="s">
         <v>10</v>
       </c>
@@ -21532,7 +21541,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="798" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="798" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B798" s="8" t="s">
         <v>5</v>
       </c>
@@ -21558,7 +21567,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="799" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="799" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B799" s="8" t="s">
         <v>5</v>
       </c>
@@ -21584,7 +21593,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="800" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="800" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B800" s="8" t="s">
         <v>10</v>
       </c>
@@ -21610,7 +21619,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="801" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="801" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B801" s="8" t="s">
         <v>5</v>
       </c>
@@ -21636,7 +21645,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="802" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="802" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B802" s="8" t="s">
         <v>10</v>
       </c>
@@ -21662,7 +21671,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="803" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="803" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B803" s="8" t="s">
         <v>5</v>
       </c>
@@ -21688,7 +21697,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="804" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="804" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B804" s="8" t="s">
         <v>10</v>
       </c>
@@ -21714,7 +21723,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="805" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="805" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B805" s="8" t="s">
         <v>10</v>
       </c>
@@ -21740,7 +21749,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="806" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="806" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B806" s="8" t="s">
         <v>5</v>
       </c>
@@ -21766,7 +21775,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="807" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="807" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B807" s="8" t="s">
         <v>5</v>
       </c>
@@ -21792,7 +21801,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="808" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="808" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B808" s="8" t="s">
         <v>5</v>
       </c>
@@ -21818,7 +21827,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="809" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="809" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B809" s="8" t="s">
         <v>10</v>
       </c>
@@ -21844,7 +21853,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="810" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="810" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B810" s="8" t="s">
         <v>5</v>
       </c>
@@ -21870,7 +21879,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="811" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="811" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B811" s="8" t="s">
         <v>5</v>
       </c>
@@ -21896,7 +21905,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="812" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="812" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B812" s="8" t="s">
         <v>10</v>
       </c>
@@ -21922,7 +21931,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="813" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="813" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B813" s="8" t="s">
         <v>10</v>
       </c>
@@ -21948,7 +21957,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="814" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="814" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B814" s="8" t="s">
         <v>10</v>
       </c>
@@ -21974,7 +21983,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="815" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="815" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B815" s="8" t="s">
         <v>10</v>
       </c>
@@ -22000,7 +22009,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="816" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="816" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B816" s="8" t="s">
         <v>5</v>
       </c>
@@ -22026,7 +22035,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="817" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="817" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B817" s="8" t="s">
         <v>10</v>
       </c>
@@ -22052,7 +22061,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="818" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="818" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B818" s="8" t="s">
         <v>5</v>
       </c>
@@ -22078,7 +22087,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="819" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="819" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B819" s="8" t="s">
         <v>10</v>
       </c>
@@ -22104,7 +22113,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="820" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="820" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B820" s="8" t="s">
         <v>5</v>
       </c>
@@ -22130,7 +22139,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="821" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="821" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B821" s="8" t="s">
         <v>10</v>
       </c>
@@ -22156,7 +22165,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="822" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="822" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B822" s="8" t="s">
         <v>5</v>
       </c>
@@ -22182,7 +22191,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="823" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="823" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B823" s="8" t="s">
         <v>5</v>
       </c>
@@ -22208,7 +22217,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="824" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="824" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B824" s="8" t="s">
         <v>5</v>
       </c>
@@ -22234,7 +22243,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="825" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="825" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B825" s="8" t="s">
         <v>5</v>
       </c>
@@ -22260,7 +22269,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="826" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="826" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B826" s="8" t="s">
         <v>10</v>
       </c>
@@ -22286,7 +22295,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="827" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="827" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B827" s="8" t="s">
         <v>5</v>
       </c>
@@ -22312,7 +22321,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="828" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="828" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B828" s="8" t="s">
         <v>5</v>
       </c>
@@ -22338,7 +22347,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="829" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="829" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B829" s="8" t="s">
         <v>10</v>
       </c>
@@ -22364,7 +22373,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="830" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="830" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B830" s="8" t="s">
         <v>5</v>
       </c>
@@ -22390,7 +22399,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="831" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="831" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B831" s="8" t="s">
         <v>5</v>
       </c>
@@ -22416,7 +22425,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="832" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="832" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B832" s="8" t="s">
         <v>5</v>
       </c>
@@ -22442,7 +22451,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="833" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="833" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B833" s="8" t="s">
         <v>10</v>
       </c>
@@ -22468,7 +22477,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="834" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="834" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B834" s="8" t="s">
         <v>5</v>
       </c>
@@ -22494,7 +22503,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="835" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="835" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B835" s="8" t="s">
         <v>5</v>
       </c>
@@ -22520,7 +22529,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="836" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="836" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B836" s="8" t="s">
         <v>10</v>
       </c>
@@ -22546,7 +22555,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="837" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="837" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B837" s="8" t="s">
         <v>5</v>
       </c>
@@ -22572,7 +22581,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="838" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="838" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B838" s="8" t="s">
         <v>10</v>
       </c>
@@ -22598,7 +22607,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="839" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="839" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B839" s="8" t="s">
         <v>5</v>
       </c>
@@ -22624,7 +22633,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="840" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="840" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B840" s="8" t="s">
         <v>10</v>
       </c>
@@ -22650,7 +22659,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="841" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="841" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B841" s="8" t="s">
         <v>5</v>
       </c>
@@ -22676,7 +22685,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="842" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="842" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B842" s="8" t="s">
         <v>10</v>
       </c>
@@ -22702,7 +22711,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="843" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="843" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B843" s="8" t="s">
         <v>5</v>
       </c>
@@ -22728,7 +22737,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="844" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="844" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B844" s="8" t="s">
         <v>5</v>
       </c>
@@ -22754,7 +22763,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="845" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="845" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B845" s="8" t="s">
         <v>10</v>
       </c>
@@ -22780,7 +22789,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="846" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="846" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B846" s="8" t="s">
         <v>5</v>
       </c>
@@ -22806,7 +22815,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="847" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="847" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B847" s="8" t="s">
         <v>10</v>
       </c>
@@ -22832,7 +22841,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="848" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="848" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B848" s="8" t="s">
         <v>5</v>
       </c>
@@ -22858,7 +22867,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="849" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="849" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B849" s="8" t="s">
         <v>10</v>
       </c>
@@ -22884,7 +22893,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="850" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="850" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B850" s="8" t="s">
         <v>10</v>
       </c>
@@ -22910,7 +22919,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="851" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="851" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B851" s="8" t="s">
         <v>10</v>
       </c>
@@ -22936,7 +22945,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="852" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="852" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B852" s="8" t="s">
         <v>5</v>
       </c>
@@ -22962,7 +22971,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="853" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="853" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B853" s="8" t="s">
         <v>10</v>
       </c>
@@ -22988,7 +22997,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="854" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="854" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B854" s="8" t="s">
         <v>10</v>
       </c>
@@ -23014,7 +23023,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="855" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="855" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B855" s="8" t="s">
         <v>5</v>
       </c>
@@ -23040,7 +23049,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="856" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="856" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B856" s="8" t="s">
         <v>5</v>
       </c>
@@ -23066,7 +23075,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="857" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="857" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B857" s="8" t="s">
         <v>10</v>
       </c>
@@ -23092,7 +23101,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="858" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="858" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B858" s="8" t="s">
         <v>10</v>
       </c>
@@ -23118,7 +23127,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="859" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="859" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B859" s="8" t="s">
         <v>5</v>
       </c>
@@ -23144,7 +23153,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="860" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="860" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B860" s="8" t="s">
         <v>10</v>
       </c>
@@ -23170,7 +23179,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="861" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="861" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B861" s="8" t="s">
         <v>5</v>
       </c>
@@ -23196,7 +23205,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="862" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="862" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B862" s="8" t="s">
         <v>10</v>
       </c>
@@ -23222,7 +23231,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="863" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="863" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B863" s="8" t="s">
         <v>10</v>
       </c>
@@ -23248,7 +23257,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="864" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="864" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B864" s="8" t="s">
         <v>5</v>
       </c>
@@ -23274,7 +23283,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="865" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="865" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B865" s="8" t="s">
         <v>5</v>
       </c>
@@ -23300,7 +23309,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="866" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="866" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B866" s="8" t="s">
         <v>10</v>
       </c>
@@ -23326,7 +23335,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="867" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="867" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B867" s="8" t="s">
         <v>5</v>
       </c>
@@ -23352,7 +23361,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="868" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="868" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B868" s="8" t="s">
         <v>10</v>
       </c>
@@ -23378,7 +23387,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="869" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="869" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B869" s="8" t="s">
         <v>10</v>
       </c>
@@ -23404,7 +23413,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="870" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="870" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B870" s="8" t="s">
         <v>10</v>
       </c>
@@ -23430,7 +23439,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="871" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="871" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B871" s="8" t="s">
         <v>10</v>
       </c>
@@ -23456,7 +23465,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="872" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="872" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B872" s="8" t="s">
         <v>10</v>
       </c>
@@ -23482,7 +23491,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="873" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="873" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B873" s="8" t="s">
         <v>10</v>
       </c>
@@ -23508,7 +23517,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="874" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="874" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B874" s="8" t="s">
         <v>10</v>
       </c>
@@ -23534,7 +23543,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="875" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="875" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B875" s="8" t="s">
         <v>5</v>
       </c>
@@ -23560,7 +23569,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="876" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="876" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B876" s="8" t="s">
         <v>10</v>
       </c>
@@ -23586,7 +23595,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="877" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="877" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B877" s="8" t="s">
         <v>10</v>
       </c>
@@ -23612,7 +23621,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="878" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="878" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B878" s="8" t="s">
         <v>5</v>
       </c>
@@ -23638,7 +23647,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="879" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="879" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B879" s="8" t="s">
         <v>10</v>
       </c>
@@ -23664,7 +23673,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="880" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="880" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B880" s="8" t="s">
         <v>10</v>
       </c>
@@ -23690,7 +23699,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="881" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="881" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B881" s="8" t="s">
         <v>10</v>
       </c>
@@ -23716,7 +23725,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="882" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="882" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B882" s="8" t="s">
         <v>5</v>
       </c>
@@ -23742,7 +23751,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="883" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="883" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B883" s="8" t="s">
         <v>5</v>
       </c>
@@ -23768,7 +23777,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="884" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="884" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B884" s="8" t="s">
         <v>10</v>
       </c>
@@ -23794,7 +23803,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="885" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="885" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B885" s="8" t="s">
         <v>5</v>
       </c>
@@ -23820,7 +23829,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="886" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="886" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B886" s="8" t="s">
         <v>5</v>
       </c>
@@ -23846,7 +23855,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="887" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="887" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B887" s="8" t="s">
         <v>10</v>
       </c>
@@ -23872,7 +23881,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="888" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="888" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B888" s="8" t="s">
         <v>5</v>
       </c>
@@ -23898,7 +23907,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="889" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="889" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B889" s="8" t="s">
         <v>5</v>
       </c>
@@ -23924,7 +23933,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="890" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="890" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B890" s="8" t="s">
         <v>5</v>
       </c>
@@ -23950,7 +23959,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="891" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="891" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B891" s="8" t="s">
         <v>10</v>
       </c>
@@ -23976,7 +23985,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="892" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="892" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B892" s="8" t="s">
         <v>5</v>
       </c>
@@ -24002,7 +24011,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="893" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="893" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B893" s="8" t="s">
         <v>10</v>
       </c>
@@ -24028,7 +24037,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="894" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="894" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B894" s="8" t="s">
         <v>5</v>
       </c>
@@ -24054,7 +24063,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="895" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="895" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B895" s="8" t="s">
         <v>5</v>
       </c>
@@ -24080,7 +24089,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="896" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="896" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B896" s="8" t="s">
         <v>5</v>
       </c>
@@ -24106,7 +24115,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="897" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="897" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B897" s="8" t="s">
         <v>10</v>
       </c>
@@ -24132,7 +24141,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="898" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="898" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B898" s="8" t="s">
         <v>5</v>
       </c>
@@ -24158,7 +24167,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="899" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="899" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B899" s="8" t="s">
         <v>5</v>
       </c>
@@ -24184,7 +24193,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="900" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="900" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B900" s="8" t="s">
         <v>10</v>
       </c>
@@ -24210,7 +24219,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="901" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="901" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B901" s="8" t="s">
         <v>5</v>
       </c>
@@ -24236,7 +24245,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="902" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="902" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B902" s="8" t="s">
         <v>10</v>
       </c>
@@ -24262,7 +24271,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="903" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="903" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B903" s="8" t="s">
         <v>5</v>
       </c>
@@ -24288,7 +24297,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="904" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="904" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B904" s="8" t="s">
         <v>10</v>
       </c>
@@ -24314,7 +24323,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="905" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="905" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B905" s="8" t="s">
         <v>5</v>
       </c>
@@ -24340,7 +24349,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="906" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="906" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B906" s="8" t="s">
         <v>5</v>
       </c>
@@ -24366,7 +24375,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="907" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="907" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B907" s="8" t="s">
         <v>5</v>
       </c>
@@ -24392,7 +24401,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="908" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="908" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B908" s="8" t="s">
         <v>5</v>
       </c>
@@ -24418,7 +24427,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="909" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="909" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B909" s="8" t="s">
         <v>10</v>
       </c>
@@ -24444,7 +24453,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="910" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="910" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B910" s="8" t="s">
         <v>10</v>
       </c>
@@ -24470,7 +24479,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="911" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="911" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B911" s="8" t="s">
         <v>5</v>
       </c>
@@ -24496,7 +24505,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="912" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="912" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B912" s="8" t="s">
         <v>5</v>
       </c>
@@ -24522,7 +24531,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="913" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="913" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B913" s="8" t="s">
         <v>10</v>
       </c>
@@ -24548,7 +24557,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="914" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="914" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B914" s="8" t="s">
         <v>10</v>
       </c>
@@ -24574,7 +24583,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="915" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="915" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B915" s="8" t="s">
         <v>5</v>
       </c>
@@ -24600,7 +24609,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="916" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="916" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B916" s="8" t="s">
         <v>5</v>
       </c>
@@ -24626,7 +24635,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="917" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="917" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B917" s="8" t="s">
         <v>5</v>
       </c>
@@ -24652,7 +24661,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="918" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="918" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B918" s="8" t="s">
         <v>5</v>
       </c>
@@ -24678,7 +24687,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="919" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="919" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B919" s="8" t="s">
         <v>5</v>
       </c>
@@ -24704,7 +24713,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="920" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="920" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B920" s="8" t="s">
         <v>10</v>
       </c>
@@ -24730,7 +24739,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="921" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="921" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B921" s="8" t="s">
         <v>5</v>
       </c>
@@ -24756,7 +24765,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="922" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="922" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B922" s="8" t="s">
         <v>5</v>
       </c>
@@ -24782,7 +24791,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="923" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="923" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B923" s="8" t="s">
         <v>10</v>
       </c>
@@ -24808,7 +24817,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="924" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="924" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B924" s="8" t="s">
         <v>10</v>
       </c>
@@ -24834,7 +24843,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="925" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="925" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B925" s="8" t="s">
         <v>5</v>
       </c>
@@ -24860,7 +24869,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="926" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="926" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B926" s="8" t="s">
         <v>10</v>
       </c>
@@ -24886,7 +24895,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="927" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="927" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B927" s="8" t="s">
         <v>5</v>
       </c>
@@ -24912,7 +24921,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="928" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="928" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B928" s="8" t="s">
         <v>10</v>
       </c>
@@ -24938,7 +24947,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="929" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="929" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B929" s="8" t="s">
         <v>10</v>
       </c>
@@ -24964,7 +24973,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="930" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="930" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B930" s="8" t="s">
         <v>10</v>
       </c>
@@ -24990,7 +24999,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="931" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="931" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B931" s="8" t="s">
         <v>5</v>
       </c>
@@ -25016,7 +25025,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="932" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="932" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B932" s="8" t="s">
         <v>10</v>
       </c>
@@ -25042,7 +25051,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="933" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="933" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B933" s="8" t="s">
         <v>5</v>
       </c>
@@ -25068,7 +25077,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="934" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="934" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B934" s="8" t="s">
         <v>10</v>
       </c>
@@ -25094,7 +25103,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="935" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="935" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B935" s="8" t="s">
         <v>10</v>
       </c>
@@ -25120,7 +25129,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="936" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="936" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B936" s="8" t="s">
         <v>10</v>
       </c>
@@ -25146,7 +25155,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="937" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="937" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B937" s="8" t="s">
         <v>10</v>
       </c>
@@ -25172,7 +25181,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="938" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="938" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B938" s="8" t="s">
         <v>10</v>
       </c>
@@ -25198,7 +25207,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="939" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="939" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B939" s="8" t="s">
         <v>10</v>
       </c>
@@ -25224,7 +25233,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="940" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="940" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B940" s="8" t="s">
         <v>10</v>
       </c>
@@ -25250,7 +25259,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="941" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="941" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B941" s="8" t="s">
         <v>5</v>
       </c>
@@ -25276,7 +25285,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="942" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="942" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B942" s="8" t="s">
         <v>10</v>
       </c>
@@ -25302,7 +25311,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="943" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="943" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B943" s="8" t="s">
         <v>10</v>
       </c>
@@ -25328,7 +25337,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="944" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="944" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B944" s="8" t="s">
         <v>10</v>
       </c>
@@ -25354,7 +25363,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="945" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="945" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B945" s="8" t="s">
         <v>5</v>
       </c>
@@ -25380,7 +25389,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="946" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="946" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B946" s="8" t="s">
         <v>10</v>
       </c>
@@ -25406,7 +25415,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="947" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="947" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B947" s="8" t="s">
         <v>10</v>
       </c>
@@ -25432,7 +25441,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="948" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="948" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B948" s="8" t="s">
         <v>5</v>
       </c>
@@ -25458,7 +25467,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="949" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="949" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B949" s="8" t="s">
         <v>5</v>
       </c>
@@ -25484,7 +25493,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="950" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="950" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B950" s="8" t="s">
         <v>10</v>
       </c>
@@ -25510,7 +25519,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="951" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="951" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B951" s="8" t="s">
         <v>5</v>
       </c>
@@ -25536,7 +25545,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="952" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="952" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B952" s="8" t="s">
         <v>10</v>
       </c>
@@ -25562,7 +25571,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="953" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="953" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B953" s="8" t="s">
         <v>5</v>
       </c>
@@ -25588,7 +25597,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="954" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="954" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B954" s="8" t="s">
         <v>10</v>
       </c>
@@ -25614,7 +25623,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="955" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="955" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B955" s="8" t="s">
         <v>5</v>
       </c>
@@ -25640,7 +25649,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="956" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="956" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B956" s="8" t="s">
         <v>5</v>
       </c>
@@ -25666,7 +25675,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="957" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="957" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B957" s="8" t="s">
         <v>10</v>
       </c>
@@ -25692,7 +25701,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="958" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="958" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B958" s="8" t="s">
         <v>5</v>
       </c>
@@ -25718,7 +25727,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="959" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="959" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B959" s="8" t="s">
         <v>10</v>
       </c>
@@ -25744,7 +25753,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="960" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="960" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B960" s="8" t="s">
         <v>10</v>
       </c>
@@ -25770,7 +25779,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="961" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="961" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B961" s="8" t="s">
         <v>5</v>
       </c>
@@ -25796,7 +25805,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="962" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="962" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B962" s="8" t="s">
         <v>5</v>
       </c>
@@ -25822,7 +25831,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="963" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="963" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B963" s="8" t="s">
         <v>10</v>
       </c>
@@ -25848,7 +25857,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="964" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="964" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B964" s="8" t="s">
         <v>5</v>
       </c>
@@ -25874,7 +25883,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="965" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="965" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B965" s="8" t="s">
         <v>5</v>
       </c>
@@ -25900,7 +25909,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="966" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="966" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B966" s="8" t="s">
         <v>5</v>
       </c>
@@ -25926,7 +25935,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="967" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="967" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B967" s="8" t="s">
         <v>5</v>
       </c>
@@ -25952,7 +25961,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="968" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="968" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B968" s="8" t="s">
         <v>10</v>
       </c>
@@ -25978,7 +25987,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="969" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="969" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B969" s="8" t="s">
         <v>5</v>
       </c>
@@ -26004,7 +26013,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="970" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="970" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B970" s="8" t="s">
         <v>10</v>
       </c>
@@ -26030,7 +26039,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="971" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="971" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B971" s="8" t="s">
         <v>10</v>
       </c>
@@ -26056,7 +26065,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="972" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="972" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B972" s="8" t="s">
         <v>5</v>
       </c>
@@ -26082,7 +26091,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="973" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="973" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B973" s="8" t="s">
         <v>5</v>
       </c>
@@ -26108,7 +26117,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="974" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="974" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B974" s="8" t="s">
         <v>5</v>
       </c>
@@ -26134,7 +26143,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="975" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="975" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B975" s="8" t="s">
         <v>10</v>
       </c>
@@ -26160,7 +26169,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="976" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="976" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B976" s="8" t="s">
         <v>5</v>
       </c>
@@ -26186,7 +26195,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="977" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="977" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B977" s="8" t="s">
         <v>5</v>
       </c>
@@ -26212,7 +26221,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="978" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="978" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B978" s="8" t="s">
         <v>5</v>
       </c>
@@ -26238,7 +26247,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="979" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="979" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B979" s="8" t="s">
         <v>5</v>
       </c>
@@ -26264,7 +26273,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="980" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="980" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B980" s="8" t="s">
         <v>10</v>
       </c>
@@ -26290,7 +26299,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="981" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="981" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B981" s="8" t="s">
         <v>10</v>
       </c>
@@ -26316,7 +26325,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="982" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="982" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B982" s="8" t="s">
         <v>10</v>
       </c>
@@ -26342,7 +26351,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="983" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="983" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B983" s="8" t="s">
         <v>5</v>
       </c>
@@ -26368,7 +26377,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="984" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="984" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B984" s="8" t="s">
         <v>5</v>
       </c>
@@ -26394,7 +26403,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="985" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="985" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B985" s="8" t="s">
         <v>10</v>
       </c>
@@ -26420,7 +26429,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="986" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="986" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B986" s="8" t="s">
         <v>10</v>
       </c>
@@ -26446,7 +26455,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="987" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="987" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B987" s="8" t="s">
         <v>5</v>
       </c>
@@ -26472,7 +26481,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="988" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="988" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B988" s="8" t="s">
         <v>5</v>
       </c>
@@ -26498,7 +26507,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="989" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="989" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B989" s="8" t="s">
         <v>10</v>
       </c>
@@ -26524,7 +26533,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="990" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="990" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B990" s="8" t="s">
         <v>5</v>
       </c>
@@ -26550,7 +26559,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="991" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="991" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B991" s="8" t="s">
         <v>10</v>
       </c>
@@ -26576,7 +26585,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="992" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="992" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B992" s="8" t="s">
         <v>5</v>
       </c>
@@ -26602,7 +26611,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="993" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="993" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B993" s="8" t="s">
         <v>5</v>
       </c>
@@ -26628,7 +26637,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="994" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="994" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B994" s="8" t="s">
         <v>10</v>
       </c>
@@ -26654,7 +26663,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="995" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="995" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B995" s="8" t="s">
         <v>5</v>
       </c>
@@ -26680,7 +26689,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="996" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="996" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B996" s="8" t="s">
         <v>5</v>
       </c>
@@ -26706,7 +26715,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="997" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="997" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B997" s="8" t="s">
         <v>5</v>
       </c>
@@ -26732,7 +26741,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="998" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="998" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B998" s="8" t="s">
         <v>10</v>
       </c>
@@ -26758,7 +26767,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="999" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="999" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B999" s="8" t="s">
         <v>5</v>
       </c>
@@ -26784,7 +26793,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="1000" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1000" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1000" s="8" t="s">
         <v>10</v>
       </c>
@@ -26810,7 +26819,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1001" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1001" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1001" s="8" t="s">
         <v>5</v>
       </c>
@@ -26836,7 +26845,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="1002" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1002" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1002" s="8" t="s">
         <v>5</v>
       </c>
@@ -26862,7 +26871,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="1003" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1003" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1003" s="7" t="s">
         <v>5</v>
       </c>
